--- a/ch_07_forecasting_time_series/ch_07_solutions.xlsx
+++ b/ch_07_forecasting_time_series/ch_07_solutions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\python-in-excel-book-staging\new_datasets\ch_07_forecasting_time_series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC34E670-A460-41A1-8B20-90823470D786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F4B359-EC80-4FE3-986A-16A0431C0B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" firstSheet="2" activeTab="3" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
@@ -50,7 +50,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="45">
+  <futureMetadata name="XLRICHVALUE" count="42">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -229,6 +229,20 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="37"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="38"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="25"/>
         </ext>
       </extLst>
@@ -243,6 +257,27 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="39"/>
         </ext>
       </extLst>
@@ -257,41 +292,6 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="27"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="28"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="29"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="30"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="31"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="41"/>
         </ext>
       </extLst>
@@ -345,34 +345,13 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="49"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="50"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="51"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="45">
+  <valueMetadata count="42">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -498,15 +477,6 @@
     </bk>
     <bk>
       <rc t="2" v="41"/>
-    </bk>
-    <bk>
-      <rc t="2" v="42"/>
-    </bk>
-    <bk>
-      <rc t="2" v="43"/>
-    </bk>
-    <bk>
-      <rc t="2" v="44"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -565,12 +535,16 @@
 fitted_values.head(10)</code>
     </pythonScript>
     <pythonScript>
-      <code>forecast_periods = 24
+      <code># Forecast horizon
+forecast_periods = 24
+# Generate forecast values
 forecast = hw_fit.forecast(steps=forecast_periods)
-forecast_dates = pd.date_range(start=passengers_df.index[-1],
-                               periods=forecast_periods + 1,
-                               freq='MS')[1:]
-forecast_dates[:5]</code>
+# Create corresponding forecast dates
+forecast_dates = pd.date_range(
+    start=passengers_df.index[-1],
+    periods=forecast_periods + 1,
+    freq='MS'
+)[1:]  # skip the last observed period</code>
     </pythonScript>
     <pythonScript>
       <code>sns.lineplot(x=passengers_df.index, y=passengers_df['passengers'],
@@ -578,6 +552,42 @@
 sns.lineplot(x=forecast_dates, y=forecast.values,
              label='Holt-Winters Forecast', linewidth=2,
              linestyle='--', color='red')
+plt.ylabel('Passenger Count')
+plt.title('Airline Passengers: Holt-Winters Forecast')
+plt.grid(True, alpha=0.3)
+plt.tight_layout()</code>
+    </pythonScript>
+    <pythonScript>
+      <code># Forecast horizon
+forecast_periods = 24
+# Generate forecast values
+forecast = hw_fit.forecast(steps=forecast_periods)
+# Create corresponding forecast dates
+forecast_dates = pd.date_range(
+    start=passengers_df.index[-1],
+    periods=forecast_periods + 1,
+    freq='MS'
+)[1:]  # skip the last observed period
+forecast_dates</code>
+    </pythonScript>
+    <pythonScript>
+      <code># Plot historical data
+sns.lineplot(
+    x=passengers_df.index,
+    y=passengers_df['passengers'],
+    label='Historical Data',
+    linewidth=2
+)
+# Plot forecast
+sns.lineplot(
+    x=forecast_dates,
+    y=forecast.values,
+    label='Holt-Winters Forecast',
+    linewidth=2,
+    linestyle='--',
+    color='red'
+)
+# Chart formatting
 plt.ylabel('Passenger Count')
 plt.title('Airline Passengers: Holt-Winters Forecast')
 plt.grid(True, alpha=0.3)
@@ -593,16 +603,25 @@
 results_df</code>
     </pythonScript>
     <pythonScript>
-      <code>train_data = passengers_df[passengers_df.index &lt; '1959-01-01']
-test_data = passengers_df[(passengers_df.index &gt;= '1959-01-01') &amp;
-                          (passengers_df.index &lt; '1961-01-01')]</code>
+      <code xml:space="preserve"># Split data into training and test sets 
+train_data = passengers_df[ 
+passengers_df.index &lt; '1959-01-01' 
+] 
+test_data = passengers_df[ 
+(passengers_df.index &gt;= '1959-01-01') &amp; 
+(passengers_df.index &lt; '1961-01-01') 
+] </code>
     </pythonScript>
     <pythonScript>
-      <code>hw_model_train = ExponentialSmoothing(train_data['passengers'],
-                                       trend='add',
-                                       seasonal='add',
-                                       seasonal_periods=12)
-hw_fit_train = hw_model_train.fit()</code>
+      <code xml:space="preserve"># Initialize Holt-Winters model on training data 
+hw_model_train = ExponentialSmoothing( 
+train_data['passengers'], 
+trend='add', 
+seasonal='add', 
+seasonal_periods=12 
+) 
+# Fit the model 
+hw_fit_train = hw_model_train.fit() </code>
     </pythonScript>
     <pythonScript>
       <code>forecast_test = hw_fit_train.forecast(steps=len(test_data))
@@ -622,9 +641,18 @@
 comparison_df</code>
     </pythonScript>
     <pythonScript>
-      <code>baseline_forecast = np.repeat(train_data['passengers'].iloc[-1], len(test_data))
-baseline_errors = np.abs(baseline_forecast - test_data['passengers'].values)
-baseline_mae = np.mean(baseline_errors)</code>
+      <code xml:space="preserve"># Create a naive baseline forecast using the last observed value 
+baseline_forecast = np.repeat( 
+train_data['passengers'].iloc[-1], 
+len(test_data) 
+) 
+# Compute absolute errors 
+baseline_errors = np.abs( 
+baseline_forecast - test_data['passengers'].values 
+) 
+# Calculate Mean Absolute Error (MAE) 
+baseline_mae = np.mean(baseline_errors) 
+</code>
     </pythonScript>
     <pythonScript>
       <code>hw_improvement = (baseline_mae - mae) / baseline_mae * 100
@@ -654,22 +682,35 @@
 shampoo_df.head()</code>
     </pythonScript>
     <pythonScript>
-      <code>sns.lineplot(x=passengers_df.index, y=passengers_df['passengers'],
-             linewidth=2)
-plt.title('Airline Passengers')
-plt.ylabel('Count')
-plt.grid(True, alpha=0.3)</code>
+      <code xml:space="preserve"># Create side-by-side subplots 
+fig, axes = plt.subplots(nrows=1, ncols=2, figsize=(12, 4)) 
+# Plot airline passengers 
+sns.lineplot( 
+x=passengers_df.index, 
+y=passengers_df['passengers'], 
+linewidth=2, 
+ax=axes[0] 
+) 
+axes[0].set_title('Airline Passengers') 
+axes[0].set_ylabel('Count') 
+axes[0].grid(True, alpha=0.3) 
+# Plot shampoo sales 
+sns.lineplot( 
+x=shampoo_df.index, 
+y=shampoo_df['sales'], 
+color='green', 
+linewidth=2, 
+ax=axes[1] 
+) 
+axes[1].set_title('Shampoo Sales') 
+axes[1].set_ylabel('Sales') 
+axes[1].grid(True, alpha=0.3) 
+# Adjust layout 
+plt.tight_layout() 
+ </code>
     </pythonScript>
     <pythonScript>
-      <code>sns.lineplot(x=shampoo_df.index, y=shampoo_df['sales'],
-             color='green', linewidth=2)
-plt.title('Shampoo Sales')
-plt.ylabel('Sales')
-plt.grid(True, alpha=0.3)</code>
-    </pythonScript>
-    <pythonScript>
-      <code>from statsmodels.tsa.seasonal import seasonal_decompose
-shampoo_decomp = seasonal_decompose(shampoo_df['sales'], model='additive', period=12)
+      <code>shampoo_decomp = seasonal_decompose(shampoo_df['sales'], model='additive', period=12)
 shampoo_decomp.plot()
 plt.suptitle('Shampoo Sales Decomposition')
 plt.tight_layout()</code>
@@ -1612,7 +1653,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1620,6 +1661,8 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1695,8 +1738,8 @@
       <xdr:rowOff>254001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>814787</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>539620</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>857</xdr:rowOff>
     </xdr:to>
@@ -1740,14 +1783,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>14111</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>793619</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>50244</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>518453</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>64355</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1762,7 +1805,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A74"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A68"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1775,7 +1818,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="22147388"/>
+          <a:off x="0" y="19430999"/>
           <a:ext cx="5760731" cy="4297689"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1788,15 +1831,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1524000</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>261054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>793619</xdr:colOff>
-      <xdr:row>147</xdr:row>
-      <xdr:rowOff>50244</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>81009</xdr:colOff>
+      <xdr:row>143</xdr:row>
+      <xdr:rowOff>7909</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1811,7 +1854,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A134"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A128"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1824,7 +1867,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="40350722"/>
+          <a:off x="1524000" y="39094832"/>
           <a:ext cx="5760731" cy="4297689"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1842,63 +1885,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>293634</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>179840</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BA76791-42A1-35B5-C5C5-D13577CC8B3D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A10"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="2743200"/>
-          <a:ext cx="5221234" cy="4142240"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
       <xdr:colOff>795867</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>8467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>637721</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>84676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1914,13 +1908,13 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A36"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A24"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1941,21 +1935,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>476515</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>179840</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>53982</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>228889</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="Image generated by Python">
+        <xdr:cNvPr id="3" name="Picture 2" descr="Image generated by Python">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FB23F7B-D9FB-06A2-9D2C-6A69F2D2FA1D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD7E82C-8FB0-598D-7934-A5F67574A01E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1963,21 +1957,21 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A26"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A10"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="7620000"/>
-          <a:ext cx="5404115" cy="4142240"/>
+          <a:off x="0" y="2730500"/>
+          <a:ext cx="10863094" cy="3566167"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2036,193 +2030,191 @@
     <v t="s">passengers</v>
     <v t="s">date</v>
     <v t="s"/>
+    <v t="r">25</v>
+    <v>360</v>
+    <v t="r">26</v>
+    <v>342</v>
     <v t="r">27</v>
-    <v>360</v>
+    <v>406</v>
     <v t="r">28</v>
-    <v>342</v>
+    <v>396</v>
     <v t="r">29</v>
-    <v>406</v>
-    <v t="r">30</v>
-    <v>396</v>
-    <v t="r">31</v>
     <v>420</v>
     <v t="s">...</v>
     <v t="s">...</v>
+    <v t="r">30</v>
+    <v>606</v>
+    <v t="r">31</v>
+    <v>508</v>
     <v t="r">32</v>
-    <v>606</v>
+    <v>461</v>
     <v t="r">33</v>
-    <v>508</v>
+    <v>390</v>
     <v t="r">34</v>
-    <v>461</v>
-    <v t="r">35</v>
-    <v>390</v>
-    <v t="r">36</v>
     <v>432</v>
   </a>
 </arrayData>
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="52">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="49">
   <rv s="0">
+    <v>14</v>
+  </rv>
+  <rv s="1">
     <fb>17899</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17930</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17958</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17989</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18019</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17988</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18079</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18171</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18263</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18353</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18050</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18080</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18111</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18142</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18172</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18203</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18233</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18264</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18295</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18323</fb>
     <v>0</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>0</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="0">
-    <fb>22282</fb>
-    <v>0</v>
+  <rv s="3">
+    <v>&lt;class 'pandas.core.indexes.datetimes.DatetimeIndex'&gt;</v>
+    <v>DatetimeIndex</v>
+    <v>DatetimeIndex(['1961-01-01', '1961-02-01', '1961-03-01', '1961-04-01',
+               '1961-05-01', '1961-06-01', '1961-07-01', '1961-08-01',
+               '1961-09-01', '1961-10-01', '1961-11-01', '1961-12-01',
+               '1962-01-01', '1962-02-0...</v>
+    <v>1</v>
   </rv>
-  <rv s="0">
-    <fb>22313</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>22341</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>22372</fb>
-    <v>0</v>
-  </rv>
-  <rv s="0">
-    <fb>22402</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
+  <rv s="2">
     <v>1</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="0">
+  <rv s="4">
+    <v>0</v>
+    <v>8</v>
+    <v>23</v>
+    <v>1</v>
+  </rv>
+  <rv s="1">
     <fb>21551</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21582</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21610</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21641</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21671</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22129</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22160</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22190</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22221</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22251</fb>
     <v>0</v>
   </rv>
-  <rv s="2">
+  <rv s="5">
     <v>0</v>
   </rv>
-  <rv s="3">
+  <rv s="6">
     <v>DataFrame</v>
-    <v>2</v>
-    <v>37</v>
+    <v>3</v>
+    <v>35</v>
   </rv>
-  <rv s="4">
+  <rv s="7">
     <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
     <v>DataFrame</v>
     <v xml:space="preserve">            passengers
@@ -2236,68 +2228,63 @@
 1959-07-01         548
 1959-08-01         559
 1959-09-01         463...</v>
-    <v>38</v>
-    <v>3</v>
+    <v>36</v>
+    <v>1</v>
   </rv>
-  <rv s="5">
+  <rv s="3">
     <v>&lt;class 'statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper'&gt;</v>
     <v>HoltWintersResultsWrapper</v>
-    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7fec3afb83e0&gt;</v>
-    <v>3</v>
+    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f180cf34110&gt;</v>
+    <v>1</v>
   </rv>
-  <rv s="6">
+  <rv s="8">
     <fb t="s">Mean Absolute Error: 31.07</fb>
     <v>&lt;class 'str'&gt;</v>
     <v>str</v>
     <v>Mean Absolute Error: 31.07</v>
     <v>Mean Absolute Error: 31.07</v>
-    <v>3</v>
+    <v>1</v>
   </rv>
-  <rv s="7">
+  <rv s="9">
     <fb>115.25</fb>
     <v>&lt;class 'numpy.float64'&gt;</v>
     <v>float64</v>
     <v>115.25</v>
     <v>115.25</v>
-    <v>3</v>
+    <v>1</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>2</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36526</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36557</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36586</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36617</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36647</fb>
     <v>0</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>3</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>4</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
-  <rv s="1">
-    <v>5</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
@@ -2305,7 +2292,10 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+  </s>
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
   </s>
@@ -2313,6 +2303,18 @@
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
     <k n="CalcOrigin" t="i"/>
     <k n="Text" t="s"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_array">
     <k n="array" t="a"/>
@@ -2327,12 +2329,6 @@
     <k n="Python_typeName" t="s"/>
     <k n="Python_str" t="s"/>
     <k n="preview" t="r"/>
-    <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
     <k n="_Provider" t="spb"/>
   </s>
   <s t="_python">
@@ -2359,19 +2355,19 @@
       <v>1</v>
     </spb>
     <spb s="1">
+      <v>https://www.anaconda.com/excel</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
+      <v>Python provided by Anaconda</v>
+    </spb>
+    <spb s="2">
       <v>24</v>
       <v>1</v>
       <v>DataFrame</v>
       <v>arrayPreview</v>
       <v>1</v>
     </spb>
-    <spb s="2">
-      <v>1</v>
-    </spb>
     <spb s="3">
-      <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
-      <v>Python provided by Anaconda</v>
+      <v>2</v>
     </spb>
   </spbData>
 </supportingPropertyBags>
@@ -2383,6 +2379,11 @@
     <k n="_Self" t="i"/>
   </s>
   <s>
+    <k n="link" t="s"/>
+    <k n="logo" t="s"/>
+    <k n="name" t="s"/>
+  </s>
+  <s>
     <k n="drw" t="i"/>
     <k n="dcol" t="i"/>
     <k n="name" t="s"/>
@@ -2391,11 +2392,6 @@
   </s>
   <s>
     <k n="ArrayCardInfo" t="spb"/>
-  </s>
-  <s>
-    <k n="link" t="s"/>
-    <k n="logo" t="s"/>
-    <k n="name" t="s"/>
   </s>
 </spbStructures>
 </file>
@@ -2420,7 +2416,6 @@
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
-  <rel r:id="rId6"/>
 </richValueRels>
 </file>
 
@@ -3940,659 +3935,792 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D059EF-DBD7-449D-AE98-3E439228E9FA}">
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
-    <col min="1" max="1" width="25.14453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.92578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.73828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A1" s="3" t="str" cm="1">
-        <f t="array" ref="A1:B7">_xlfn._xlws.PY(0,0,passengers[#All])</f>
+        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(0,0,passengers[#All])</f>
         <v/>
       </c>
       <c r="B1" t="str">
+        <f ca="1"/>
         <v>passengers</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A2" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B2" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A3" s="3" vm="1">
+      <c r="A3" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
       <c r="B3">
+        <f ca="1"/>
         <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A4" s="3" vm="2">
+      <c r="A4" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
       <c r="B4">
+        <f ca="1"/>
         <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A5" s="3" vm="3">
+      <c r="A5" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
       <c r="B5">
+        <f ca="1"/>
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A6" s="3" vm="4">
+      <c r="A6" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
       <c r="B6">
+        <f ca="1"/>
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A7" s="3" vm="5">
+      <c r="A7" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
       <c r="B7">
+        <f ca="1"/>
         <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A9" s="3" t="str" cm="1">
-        <f t="array" ref="A9:B15">_xlfn._xlws.PY(1,0)</f>
+        <f t="array" aca="1" ref="A9:B15" ca="1">_xlfn._xlws.PY(1,0)</f>
         <v/>
       </c>
       <c r="B9" t="str">
+        <f ca="1"/>
         <v>passengers</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A10" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B10" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A11" s="3" vm="6">
+      <c r="A11" s="3" vm="7">
+        <f ca="1"/>
         <v>17988</v>
       </c>
       <c r="B11">
+        <f ca="1"/>
         <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A12" s="3" vm="7">
+      <c r="A12" s="3" vm="8">
+        <f ca="1"/>
         <v>18079</v>
       </c>
       <c r="B12">
+        <f ca="1"/>
         <v>385</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A13" s="3" vm="8">
+      <c r="A13" s="3" vm="9">
+        <f ca="1"/>
         <v>18171</v>
       </c>
       <c r="B13">
+        <f ca="1"/>
         <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A14" s="3" vm="9">
+      <c r="A14" s="3" vm="10">
+        <f ca="1"/>
         <v>18263</v>
       </c>
       <c r="B14">
+        <f ca="1"/>
         <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A15" s="3" vm="10">
+      <c r="A15" s="3" vm="11">
+        <f ca="1"/>
         <v>18353</v>
       </c>
       <c r="B15">
+        <f ca="1"/>
         <v>382</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A18" s="3" t="str" cm="1">
-        <f t="array" ref="A18:B33">_xlfn._xlws.PY(2,0)</f>
+        <f t="array" aca="1" ref="A18:B33" ca="1">_xlfn._xlws.PY(2,0)</f>
         <v>date</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B18" s="5" t="str">
+        <f ca="1"/>
         <v>trend</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A19" s="3" vm="1">
+      <c r="A19" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
-      <c r="B19" t="e">
+      <c r="B19" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A20" s="3" vm="2">
+      <c r="A20" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
-      <c r="B20" t="e">
+      <c r="B20" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A21" s="3" vm="3">
+      <c r="A21" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
-      <c r="B21" t="e">
+      <c r="B21" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A22" s="3" vm="4">
+      <c r="A22" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
-      <c r="B22" t="e">
+      <c r="B22" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A23" s="3" vm="5">
+      <c r="A23" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
-      <c r="B23" t="e">
+      <c r="B23" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A24" s="3" vm="11">
+      <c r="A24" s="3" vm="12">
+        <f ca="1"/>
         <v>18050</v>
       </c>
-      <c r="B24" t="e">
+      <c r="B24" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A25" s="3" vm="12">
+      <c r="A25" s="3" vm="13">
+        <f ca="1"/>
         <v>18080</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="5">
+        <f ca="1"/>
         <v>126.79166666666666</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A26" s="3" vm="13">
+      <c r="A26" s="3" vm="14">
+        <f ca="1"/>
         <v>18111</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="5">
+        <f ca="1"/>
         <v>127.24999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A27" s="3" vm="14">
+      <c r="A27" s="3" vm="15">
+        <f ca="1"/>
         <v>18142</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="5">
+        <f ca="1"/>
         <v>127.95833333333331</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A28" s="3" vm="15">
+      <c r="A28" s="3" vm="16">
+        <f ca="1"/>
         <v>18172</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="5">
+        <f ca="1"/>
         <v>128.58333333333331</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A29" s="3" vm="16">
+      <c r="A29" s="3" vm="17">
+        <f ca="1"/>
         <v>18203</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="5">
+        <f ca="1"/>
         <v>128.99999999999997</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A30" s="3" vm="17">
+      <c r="A30" s="3" vm="18">
+        <f ca="1"/>
         <v>18233</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="5">
+        <f ca="1"/>
         <v>129.75</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A31" s="3" vm="18">
+      <c r="A31" s="3" vm="19">
+        <f ca="1"/>
         <v>18264</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="5">
+        <f ca="1"/>
         <v>131.25</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A32" s="3" vm="19">
+      <c r="A32" s="3" vm="20">
+        <f ca="1"/>
         <v>18295</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="5">
+        <f ca="1"/>
         <v>133.08333333333334</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A33" s="3" vm="20">
+      <c r="A33" s="3" vm="21">
+        <f ca="1"/>
         <v>18323</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="5">
+        <f ca="1"/>
         <v>134.91666666666669</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A36" s="3" t="e" cm="1" vm="21">
-        <f t="array" ref="A36">_xlfn._xlws.PY(3,0)</f>
+      <c r="A36" s="3" t="e" cm="1" vm="22">
+        <f t="array" aca="1" ref="A36" ca="1">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B51" s="6"/>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A52" s="3" t="str" cm="1">
-        <f t="array" ref="A52:B62">_xlfn._xlws.PY(4,0)</f>
+        <f t="array" aca="1" ref="A52:B62" ca="1">_xlfn._xlws.PY(4,0)</f>
         <v>date</v>
       </c>
-      <c r="B52" t="str">
+      <c r="B52" s="6" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A53" s="3" vm="1">
+      <c r="A53" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="6">
+        <f ca="1"/>
         <v>111.95999796199298</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A54" s="3" vm="2">
+      <c r="A54" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="6">
+        <f ca="1"/>
         <v>120.19333660189936</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A55" s="3" vm="3">
+      <c r="A55" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="6">
+        <f ca="1"/>
         <v>134.67683544691363</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A56" s="3" vm="4">
+      <c r="A56" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="6">
+        <f ca="1"/>
         <v>131.40726345798356</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A57" s="3" vm="5">
+      <c r="A57" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="6">
+        <f ca="1"/>
         <v>124.64374307768698</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A58" s="3" vm="11">
+      <c r="A58" s="3" vm="12">
+        <f ca="1"/>
         <v>18050</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="6">
+        <f ca="1"/>
         <v>140.4272455247596</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A59" s="3" vm="12">
+      <c r="A59" s="3" vm="13">
+        <f ca="1"/>
         <v>18080</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="6">
+        <f ca="1"/>
         <v>153.85808678698692</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A60" s="3" vm="13">
+      <c r="A60" s="3" vm="14">
+        <f ca="1"/>
         <v>18111</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="6">
+        <f ca="1"/>
         <v>152.4364177143994</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A61" s="3" vm="14">
+      <c r="A61" s="3" vm="15">
+        <f ca="1"/>
         <v>18142</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="6">
+        <f ca="1"/>
         <v>139.68358943158842</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A62" s="3" vm="15">
+      <c r="A62" s="3" vm="16">
+        <f ca="1"/>
         <v>18172</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="6">
+        <f ca="1"/>
         <v>122.38855242329556</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A67" s="3" cm="1" vm="22">
-        <f t="array" ref="A67:A71">_xlfn._xlws.PY(5,0)</f>
-        <v>22282</v>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A64" s="3" t="e" cm="1" vm="23">
+        <f t="array" aca="1" ref="A64" ca="1">_xlfn._xlws.PY(5,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A68" s="3" vm="23">
-        <v>22313</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A69" s="3" vm="24">
-        <v>22341</v>
+      <c r="A68" s="3" t="e" cm="1" vm="24">
+        <f t="array" aca="1" ref="A68" ca="1">_xlfn._xlws.PY(6,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A70" s="3" vm="25">
-        <v>22372</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A71" s="3" vm="26">
-        <v>22402</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A74" s="3" t="e" cm="1" vm="27">
-        <f t="array" ref="A74">_xlfn._xlws.PY(6,0)</f>
+      <c r="A70" s="3" t="e" cm="1" vm="25">
+        <f t="array" aca="1" ref="A70" ca="1">_xlfn._xlws.PY(7,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.85">
+      <c r="A77" s="3" t="e" cm="1" vm="24">
+        <f t="array" aca="1" ref="A77" ca="1">_xlfn._xlws.PY(8,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A85" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A85:B87" ca="1">_xlfn._xlws.PY(9,0)</f>
+        <v>Metric</v>
+      </c>
+      <c r="B85" t="str">
+        <f ca="1"/>
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A86" s="3" t="str">
+        <f ca="1"/>
+        <v>Test Statistic</v>
+      </c>
+      <c r="B86" s="6">
+        <f ca="1"/>
+        <v>0.81536887920606549</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A87" s="3" t="str">
+        <f ca="1"/>
+        <v>p-value</v>
+      </c>
+      <c r="B87" s="6">
+        <f ca="1"/>
+        <v>0.99188024343764125</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A89" s="3" t="e" cm="1" vm="26">
+        <f t="array" aca="1" ref="A89" ca="1">_xlfn._xlws.PY(10,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A91" s="3" t="str" cm="1">
-        <f t="array" ref="A91:B93">_xlfn._xlws.PY(7,0)</f>
-        <v>Metric</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A92" s="3" t="str">
-        <v>Test Statistic</v>
-      </c>
-      <c r="B92">
-        <v>0.81536887920606549</v>
+      <c r="A91" s="3" t="e" cm="1" vm="27">
+        <f t="array" aca="1" ref="A91" ca="1">_xlfn._xlws.PY(11,1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A93" s="3" t="str">
-        <v>p-value</v>
-      </c>
-      <c r="B93">
-        <v>0.99188024343764125</v>
+      <c r="A93" s="3" cm="1" vm="28">
+        <f t="array" aca="1" ref="A93:B97" ca="1">_xlfn._xlws.PY(12,0)</f>
+        <v>21551</v>
+      </c>
+      <c r="B93" s="6">
+        <f ca="1"/>
+        <v>354.17364147573602</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A94" s="3" vm="29">
+        <f ca="1"/>
+        <v>21582</v>
+      </c>
+      <c r="B94" s="6">
+        <f ca="1"/>
+        <v>337.57319653024558</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A95" s="3" t="e" cm="1" vm="28">
-        <f t="array" ref="A95">_xlfn._xlws.PY(8,1)</f>
-        <v>#VALUE!</v>
+      <c r="A95" s="3" vm="30">
+        <f ca="1"/>
+        <v>21610</v>
+      </c>
+      <c r="B95" s="6">
+        <f ca="1"/>
+        <v>387.7744448625624</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A96" s="3" vm="31">
+        <f ca="1"/>
+        <v>21641</v>
+      </c>
+      <c r="B96" s="6">
+        <f ca="1"/>
+        <v>379.77500904445122</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A97" s="3" t="e" cm="1" vm="29">
-        <f t="array" ref="A97">_xlfn._xlws.PY(9,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A99" s="3" cm="1" vm="30">
-        <f t="array" ref="A99:B103">_xlfn._xlws.PY(10,0)</f>
-        <v>21551</v>
-      </c>
-      <c r="B99">
+      <c r="A97" s="3" vm="32">
+        <f ca="1"/>
+        <v>21671</v>
+      </c>
+      <c r="B97" s="6">
+        <f ca="1"/>
+        <v>397.21314537513348</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A100" s="3" t="str" cm="1" vm="33">
+        <f t="array" aca="1" ref="A100" ca="1">_xlfn._xlws.PY(13,1)</f>
+        <v>Mean Absolute Error: 31.07</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A103" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A103:C115" ca="1">_xlfn._xlws.PY(14,0)</f>
+        <v>Actual</v>
+      </c>
+      <c r="B103" s="6" t="str">
+        <f ca="1"/>
+        <v>Forecast</v>
+      </c>
+      <c r="C103" s="6" t="str">
+        <f ca="1"/>
+        <v>Error</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A104" s="3">
+        <f ca="1"/>
+        <v>360</v>
+      </c>
+      <c r="B104" s="6">
+        <f ca="1"/>
         <v>354.17364147573602</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A100" s="3" vm="31">
-        <v>21582</v>
-      </c>
-      <c r="B100">
+      <c r="C104" s="6">
+        <f ca="1"/>
+        <v>5.8263585242639806</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A105" s="3">
+        <f ca="1"/>
+        <v>342</v>
+      </c>
+      <c r="B105" s="6">
+        <f ca="1"/>
         <v>337.57319653024558</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A101" s="3" vm="32">
-        <v>21610</v>
-      </c>
-      <c r="B101">
+      <c r="C105" s="6">
+        <f ca="1"/>
+        <v>4.4268034697544181</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A106" s="3">
+        <f ca="1"/>
+        <v>406</v>
+      </c>
+      <c r="B106" s="6">
+        <f ca="1"/>
         <v>387.7744448625624</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A102" s="3" vm="33">
-        <v>21641</v>
-      </c>
-      <c r="B102">
+      <c r="C106" s="6">
+        <f ca="1"/>
+        <v>18.225555137437595</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A107" s="3">
+        <f ca="1"/>
+        <v>396</v>
+      </c>
+      <c r="B107" s="6">
+        <f ca="1"/>
         <v>379.77500904445122</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A103" s="3" vm="34">
-        <v>21671</v>
-      </c>
-      <c r="B103">
+      <c r="C107" s="6">
+        <f ca="1"/>
+        <v>16.224990955548776</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A108" s="3">
+        <f ca="1"/>
+        <v>420</v>
+      </c>
+      <c r="B108" s="6">
+        <f ca="1"/>
         <v>397.21314537513348</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A106" s="3" t="str" cm="1" vm="35">
-        <f t="array" ref="A106">_xlfn._xlws.PY(11,1)</f>
-        <v>Mean Absolute Error: 31.07</v>
+      <c r="C108" s="6">
+        <f ca="1"/>
+        <v>22.786854624866521</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A109" s="3" t="str" cm="1">
-        <f t="array" ref="A109:C121">_xlfn._xlws.PY(12,0)</f>
-        <v>Actual</v>
-      </c>
-      <c r="B109" t="str">
-        <v>Forecast</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Error</v>
+      <c r="A109" s="3">
+        <f ca="1"/>
+        <v>472</v>
+      </c>
+      <c r="B109" s="6">
+        <f ca="1"/>
+        <v>468.87706028701018</v>
+      </c>
+      <c r="C109" s="6">
+        <f ca="1"/>
+        <v>3.1229397129898189</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.85">
       <c r="A110" s="3">
-        <v>360</v>
-      </c>
-      <c r="B110">
-        <v>354.17364147573602</v>
-      </c>
-      <c r="C110">
-        <v>5.8263585242639806</v>
+        <f ca="1"/>
+        <v>548</v>
+      </c>
+      <c r="B110" s="6">
+        <f ca="1"/>
+        <v>520.42527545650694</v>
+      </c>
+      <c r="C110" s="6">
+        <f ca="1"/>
+        <v>27.574724543493062</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.85">
       <c r="A111" s="3">
-        <v>342</v>
-      </c>
-      <c r="B111">
-        <v>337.57319653024558</v>
-      </c>
-      <c r="C111">
-        <v>4.4268034697544181</v>
+        <f ca="1"/>
+        <v>559</v>
+      </c>
+      <c r="B111" s="6">
+        <f ca="1"/>
+        <v>526.51011146486042</v>
+      </c>
+      <c r="C111" s="6">
+        <f ca="1"/>
+        <v>32.489888535139585</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.85">
       <c r="A112" s="3">
-        <v>406</v>
-      </c>
-      <c r="B112">
-        <v>387.7744448625624</v>
-      </c>
-      <c r="C112">
-        <v>18.225555137437595</v>
+        <f ca="1"/>
+        <v>463</v>
+      </c>
+      <c r="B112" s="6">
+        <f ca="1"/>
+        <v>427.87427734740862</v>
+      </c>
+      <c r="C112" s="6">
+        <f ca="1"/>
+        <v>35.125722652591378</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.85">
       <c r="A113" s="3">
-        <v>396</v>
-      </c>
-      <c r="B113">
-        <v>379.77500904445122</v>
-      </c>
-      <c r="C113">
-        <v>16.224990955548776</v>
+        <f ca="1"/>
+        <v>407</v>
+      </c>
+      <c r="B113" s="6">
+        <f ca="1"/>
+        <v>381.94210181918794</v>
+      </c>
+      <c r="C113" s="6">
+        <f ca="1"/>
+        <v>25.05789818081206</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.85">
       <c r="A114" s="3">
-        <v>420</v>
-      </c>
-      <c r="B114">
-        <v>397.21314537513348</v>
-      </c>
-      <c r="C114">
-        <v>22.786854624866521</v>
+        <f ca="1"/>
+        <v>362</v>
+      </c>
+      <c r="B114" s="6">
+        <f ca="1"/>
+        <v>334.44886906567876</v>
+      </c>
+      <c r="C114" s="6">
+        <f ca="1"/>
+        <v>27.551130934321236</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.85">
       <c r="A115" s="3">
-        <v>472</v>
-      </c>
-      <c r="B115">
-        <v>468.87706028701018</v>
-      </c>
-      <c r="C115">
-        <v>3.1229397129898189</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A116" s="3">
-        <v>548</v>
-      </c>
-      <c r="B116">
-        <v>520.42527545650694</v>
-      </c>
-      <c r="C116">
-        <v>27.574724543493062</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A117" s="3">
-        <v>559</v>
-      </c>
-      <c r="B117">
-        <v>526.51011146486042</v>
-      </c>
-      <c r="C117">
-        <v>32.489888535139585</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A118" s="3">
-        <v>463</v>
-      </c>
-      <c r="B118">
-        <v>427.87427734740862</v>
-      </c>
-      <c r="C118">
-        <v>35.125722652591378</v>
+        <f ca="1"/>
+        <v>405</v>
+      </c>
+      <c r="B115" s="6">
+        <f ca="1"/>
+        <v>373.5830131238987</v>
+      </c>
+      <c r="C115" s="6">
+        <f ca="1"/>
+        <v>31.416986876101305</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A119" s="3">
-        <v>407</v>
-      </c>
-      <c r="B119">
-        <v>381.94210181918794</v>
-      </c>
-      <c r="C119">
-        <v>25.05789818081206</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A120" s="3">
-        <v>362</v>
-      </c>
-      <c r="B120">
-        <v>334.44886906567876</v>
-      </c>
-      <c r="C120">
-        <v>27.551130934321236</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A121" s="3">
-        <v>405</v>
-      </c>
-      <c r="B121">
-        <v>373.5830131238987</v>
-      </c>
-      <c r="C121">
-        <v>31.416986876101305</v>
+      <c r="A119" s="3" cm="1" vm="34">
+        <f t="array" aca="1" ref="A119" ca="1">_xlfn._xlws.PY(15,1)</f>
+        <v>115.25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A122" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A122:B125" ca="1">_xlfn._xlws.PY(16,0)</f>
+        <v>Metric</v>
+      </c>
+      <c r="B122" t="str">
+        <f ca="1"/>
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A123" s="3" t="str">
+        <f ca="1"/>
+        <v>Holt-Winters MAE</v>
+      </c>
+      <c r="B123">
+        <f ca="1"/>
+        <v>31.07</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A124" s="3" t="str">
+        <f ca="1"/>
+        <v>Baseline MAE</v>
+      </c>
+      <c r="B124">
+        <f ca="1"/>
+        <v>115.25</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A125" s="3" cm="1" vm="36">
-        <f t="array" ref="A125">_xlfn._xlws.PY(13,1)</f>
-        <v>115.25</v>
+      <c r="A125" s="3" t="str">
+        <f ca="1"/>
+        <v>Improvement (%)</v>
+      </c>
+      <c r="B125">
+        <f ca="1"/>
+        <v>73.040000000000006</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A128" s="3" t="str" cm="1">
-        <f t="array" ref="A128:B131">_xlfn._xlws.PY(14,0)</f>
-        <v>Metric</v>
-      </c>
-      <c r="B128" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A129" s="3" t="str">
-        <v>Holt-Winters MAE</v>
-      </c>
-      <c r="B129">
-        <v>31.07</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A130" s="3" t="str">
-        <v>Baseline MAE</v>
-      </c>
-      <c r="B130">
-        <v>115.25</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A131" s="3" t="str">
-        <v>Improvement (%)</v>
-      </c>
-      <c r="B131">
-        <v>73.040000000000006</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A134" s="3" t="e" cm="1" vm="37">
-        <f t="array" ref="A134">_xlfn._xlws.PY(15,0)</f>
+      <c r="A128" s="3" t="e" cm="1" vm="35">
+        <f t="array" aca="1" ref="A128" ca="1">_xlfn._xlws.PY(17,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5132,7 +5260,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D36D00-A3A2-41DD-AB6F-6740B077CEDA}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="8.73828125" bestFit="1" customWidth="1"/>
@@ -5140,76 +5268,83 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A1" t="str" cm="1">
-        <f t="array" ref="A1:B7">_xlfn._xlws.PY(16,0,shampoo[#All])</f>
+        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(18,0,shampoo[#All])</f>
         <v/>
       </c>
       <c r="B1" t="str">
+        <f ca="1"/>
         <v>sales</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.85">
       <c r="A2" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B2" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A3" vm="38">
+      <c r="A3" vm="36">
+        <f ca="1"/>
         <v>36526</v>
       </c>
       <c r="B3">
+        <f ca="1"/>
         <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A4" vm="39">
+      <c r="A4" vm="37">
+        <f ca="1"/>
         <v>36557</v>
       </c>
       <c r="B4">
+        <f ca="1"/>
         <v>145.9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A5" vm="40">
+      <c r="A5" vm="38">
+        <f ca="1"/>
         <v>36586</v>
       </c>
       <c r="B5">
+        <f ca="1"/>
         <v>183.1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A6" vm="41">
+      <c r="A6" vm="39">
+        <f ca="1"/>
         <v>36617</v>
       </c>
       <c r="B6">
+        <f ca="1"/>
         <v>119.3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A7" vm="42">
+      <c r="A7" vm="40">
+        <f ca="1"/>
         <v>36647</v>
       </c>
       <c r="B7">
+        <f ca="1"/>
         <v>180.3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A10" t="e" cm="1" vm="43">
-        <f t="array" ref="A10">_xlfn._xlws.PY(17,0)</f>
+      <c r="A10" t="e" cm="1" vm="41">
+        <f t="array" aca="1" ref="A10" ca="1">_xlfn._xlws.PY(19,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A26" t="e" cm="1" vm="44">
-        <f t="array" ref="A26">_xlfn._xlws.PY(18,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A36" t="e" cm="1" vm="45">
-        <f t="array" ref="A36">_xlfn._xlws.PY(19,0)</f>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.85">
+      <c r="A24" t="e" cm="1" vm="42">
+        <f t="array" aca="1" ref="A24" ca="1">_xlfn._xlws.PY(20,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/ch_07_forecasting_time_series/ch_07_solutions.xlsx
+++ b/ch_07_forecasting_time_series/ch_07_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F4B359-EC80-4FE3-986A-16A0431C0B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4507EEEF-B5AF-41C4-9ACE-1E3D2FCCA916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" firstSheet="2" activeTab="3" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
@@ -50,298 +50,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="42">
+  <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="10"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="11"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="13"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="14"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="15"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="16"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="17"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="18"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="19"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="20"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="21"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="22"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="23"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="24"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="37"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="38"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="25"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="26"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="27"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="28"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="29"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="39"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="40"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="41"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="42"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="43"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="44"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="45"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="46"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="47"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="48"/>
         </ext>
       </extLst>
     </bk>
@@ -351,132 +64,9 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="42">
+  <valueMetadata count="1">
     <bk>
       <rc t="2" v="0"/>
-    </bk>
-    <bk>
-      <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
-    <bk>
-      <rc t="2" v="5"/>
-    </bk>
-    <bk>
-      <rc t="2" v="6"/>
-    </bk>
-    <bk>
-      <rc t="2" v="7"/>
-    </bk>
-    <bk>
-      <rc t="2" v="8"/>
-    </bk>
-    <bk>
-      <rc t="2" v="9"/>
-    </bk>
-    <bk>
-      <rc t="2" v="10"/>
-    </bk>
-    <bk>
-      <rc t="2" v="11"/>
-    </bk>
-    <bk>
-      <rc t="2" v="12"/>
-    </bk>
-    <bk>
-      <rc t="2" v="13"/>
-    </bk>
-    <bk>
-      <rc t="2" v="14"/>
-    </bk>
-    <bk>
-      <rc t="2" v="15"/>
-    </bk>
-    <bk>
-      <rc t="2" v="16"/>
-    </bk>
-    <bk>
-      <rc t="2" v="17"/>
-    </bk>
-    <bk>
-      <rc t="2" v="18"/>
-    </bk>
-    <bk>
-      <rc t="2" v="19"/>
-    </bk>
-    <bk>
-      <rc t="2" v="20"/>
-    </bk>
-    <bk>
-      <rc t="2" v="21"/>
-    </bk>
-    <bk>
-      <rc t="2" v="22"/>
-    </bk>
-    <bk>
-      <rc t="2" v="23"/>
-    </bk>
-    <bk>
-      <rc t="2" v="24"/>
-    </bk>
-    <bk>
-      <rc t="2" v="25"/>
-    </bk>
-    <bk>
-      <rc t="2" v="26"/>
-    </bk>
-    <bk>
-      <rc t="2" v="27"/>
-    </bk>
-    <bk>
-      <rc t="2" v="28"/>
-    </bk>
-    <bk>
-      <rc t="2" v="29"/>
-    </bk>
-    <bk>
-      <rc t="2" v="30"/>
-    </bk>
-    <bk>
-      <rc t="2" v="31"/>
-    </bk>
-    <bk>
-      <rc t="2" v="32"/>
-    </bk>
-    <bk>
-      <rc t="2" v="33"/>
-    </bk>
-    <bk>
-      <rc t="2" v="34"/>
-    </bk>
-    <bk>
-      <rc t="2" v="35"/>
-    </bk>
-    <bk>
-      <rc t="2" v="36"/>
-    </bk>
-    <bk>
-      <rc t="2" v="37"/>
-    </bk>
-    <bk>
-      <rc t="2" v="38"/>
-    </bk>
-    <bk>
-      <rc t="2" v="39"/>
-    </bk>
-    <bk>
-      <rc t="2" v="40"/>
-    </bk>
-    <bk>
-      <rc t="2" v="41"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -507,8 +97,30 @@
 passengers_df.head()</code>
     </pythonScript>
     <pythonScript>
-      <code>quarterly = passengers_df.resample('QE').sum()
+      <code>quarterly = passengers_df.resample('QE').mean()
 quarterly.head()</code>
+    </pythonScript>
+    <pythonScript>
+      <code>sns.lineplot(x=passengers_df.index, y=passengers_df['passengers'],
+             label='Monthly', alpha=0.5)
+sns.lineplot(x=quarterly.index, y=quarterly['passengers'],
+             label='Quarterly (resampled)', linewidth=2)
+plt.ylabel('Passenger Count')
+plt.title('Monthly vs Quarterly Passenger Counts')
+plt.tight_layout()</code>
+    </pythonScript>
+    <pythonScript>
+      <code xml:space="preserve">passengers_df['rolling_mean'] = passengers_df['passengers'].rolling(window=12).mean()
+passengers_df.head(12) </code>
+    </pythonScript>
+    <pythonScript>
+      <code xml:space="preserve">sns.lineplot(x=passengers_df.index, y=passengers_df['passengers'], 
+              label='Monthly passengers', alpha=0.6) 
+sns.lineplot(x=passengers_df.index, y=passengers_df['rolling_mean'], 
+              label='12-month rolling mean', linewidth=2) 
+plt.ylabel('Passenger Count') 
+plt.title('Airline Passengers with 12-Month Rolling Mean') 
+plt.tight_layout() </code>
     </pythonScript>
     <pythonScript>
       <code>from statsmodels.tsa.seasonal import seasonal_decompose
@@ -532,7 +144,9 @@
                                  seasonal_periods=12)
 hw_fit = hw_model.fit()
 fitted_values = hw_fit.fittedvalues
-fitted_values.head(10)</code>
+comparison = passengers_df[['passengers']].copy()
+comparison['fitted'] = fitted_values
+comparison.head(10)</code>
     </pythonScript>
     <pythonScript>
       <code># Forecast horizon
@@ -1734,13 +1348,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1001889</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>254001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>539620</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:colOff>144508</xdr:colOff>
+      <xdr:row>117</xdr:row>
       <xdr:rowOff>857</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1756,7 +1370,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A36"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A104"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1783,13 +1397,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>135</xdr:row>
       <xdr:rowOff>14111</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>518453</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:colOff>144509</xdr:colOff>
+      <xdr:row>149</xdr:row>
       <xdr:rowOff>64355</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1805,7 +1419,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A68"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A136"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1832,14 +1446,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1524000</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>196</xdr:row>
       <xdr:rowOff>261054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>81009</xdr:colOff>
-      <xdr:row>143</xdr:row>
-      <xdr:rowOff>7909</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>666619</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>7910</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1854,7 +1468,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A128"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A196"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1868,6 +1482,104 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1524000" y="39094832"/>
+          <a:ext cx="5760731" cy="4297689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2088445</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>91722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>141112</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>60478</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F9428AE-58BA-C0CA-4C63-230BBBCB957B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A60"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2088445" y="9800167"/>
+          <a:ext cx="5651500" cy="4216199"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>144509</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>50244</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="Image generated by Python">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7AE6D6B-4071-1EF7-9551-F0320D935CED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+          <a:extLst>
+            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="passengers_ts!A17"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4854222"/>
           <a:ext cx="5760731" cy="4297689"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2023,400 +1735,22 @@
 </rvTypesInfo>
 </file>
 
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <a r="13" c="2">
-    <v t="s"/>
-    <v t="s">passengers</v>
-    <v t="s">date</v>
-    <v t="s"/>
-    <v t="r">25</v>
-    <v>360</v>
-    <v t="r">26</v>
-    <v>342</v>
-    <v t="r">27</v>
-    <v>406</v>
-    <v t="r">28</v>
-    <v>396</v>
-    <v t="r">29</v>
-    <v>420</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="r">30</v>
-    <v>606</v>
-    <v t="r">31</v>
-    <v>508</v>
-    <v t="r">32</v>
-    <v>461</v>
-    <v t="r">33</v>
-    <v>390</v>
-    <v t="r">34</v>
-    <v>432</v>
-  </a>
-</arrayData>
-</file>
-
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="49">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <rv s="0">
-    <v>14</v>
-  </rv>
-  <rv s="1">
-    <fb>17899</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>17930</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>17958</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>17989</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18019</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>17988</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18079</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18171</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18263</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18353</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18050</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18080</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18111</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18142</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18172</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18203</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18233</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18264</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18295</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>18323</fb>
-    <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>0</v>
     <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'pandas.core.indexes.datetimes.DatetimeIndex'&gt;</v>
-    <v>DatetimeIndex</v>
-    <v>DatetimeIndex(['1961-01-01', '1961-02-01', '1961-03-01', '1961-04-01',
-               '1961-05-01', '1961-06-01', '1961-07-01', '1961-08-01',
-               '1961-09-01', '1961-10-01', '1961-11-01', '1961-12-01',
-               '1962-01-01', '1962-02-0...</v>
-    <v>1</v>
-  </rv>
-  <rv s="2">
-    <v>1</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
-  <rv s="4">
-    <v>0</v>
-    <v>8</v>
-    <v>23</v>
-    <v>1</v>
-  </rv>
-  <rv s="1">
-    <fb>21551</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>21582</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>21610</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>21641</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>21671</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>22129</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>22160</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>22190</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>22221</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>22251</fb>
-    <v>0</v>
-  </rv>
-  <rv s="5">
-    <v>0</v>
-  </rv>
-  <rv s="6">
-    <v>DataFrame</v>
-    <v>3</v>
-    <v>35</v>
-  </rv>
-  <rv s="7">
-    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
-    <v>DataFrame</v>
-    <v xml:space="preserve">            passengers
-date                  
-1959-01-01         360
-1959-02-01         342
-1959-03-01         406
-1959-04-01         396
-1959-05-01         420
-1959-06-01         472
-1959-07-01         548
-1959-08-01         559
-1959-09-01         463...</v>
-    <v>36</v>
-    <v>1</v>
-  </rv>
-  <rv s="3">
-    <v>&lt;class 'statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper'&gt;</v>
-    <v>HoltWintersResultsWrapper</v>
-    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f180cf34110&gt;</v>
-    <v>1</v>
-  </rv>
-  <rv s="8">
-    <fb t="s">Mean Absolute Error: 31.07</fb>
-    <v>&lt;class 'str'&gt;</v>
-    <v>str</v>
-    <v>Mean Absolute Error: 31.07</v>
-    <v>Mean Absolute Error: 31.07</v>
-    <v>1</v>
-  </rv>
-  <rv s="9">
-    <fb>115.25</fb>
-    <v>&lt;class 'numpy.float64'&gt;</v>
-    <v>float64</v>
-    <v>115.25</v>
-    <v>115.25</v>
-    <v>1</v>
-  </rv>
-  <rv s="2">
-    <v>2</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
-  <rv s="1">
-    <fb>36526</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>36557</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>36586</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>36617</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>36647</fb>
-    <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>3</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
+    <v>18</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <s t="_error">
     <k n="errorType" t="i"/>
-  </s>
-  <s t="_formattednumber">
-    <k n="_Format" t="spb"/>
-  </s>
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="Text" t="s"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_error">
-    <k n="colOffset" t="i"/>
-    <k n="errorType" t="i"/>
-    <k n="rwOffset" t="i"/>
     <k n="subType" t="i"/>
   </s>
-  <s t="_array">
-    <k n="array" t="a"/>
-  </s>
-  <s t="_entity">
-    <k n="_DisplayString" t="s"/>
-    <k n="_ViewInfo" t="spb"/>
-    <k n="arrayPreview" t="r"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="preview" t="r"/>
-    <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="basicValue" t="s"/>
-    <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="basicValue"/>
-    <k n="_Provider" t="spb"/>
-  </s>
 </rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="4">
-    <spb s="0">
-      <v>1</v>
-    </spb>
-    <spb s="1">
-      <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
-      <v>Python provided by Anaconda</v>
-    </spb>
-    <spb s="2">
-      <v>24</v>
-      <v>1</v>
-      <v>DataFrame</v>
-      <v>arrayPreview</v>
-      <v>1</v>
-    </spb>
-    <spb s="3">
-      <v>2</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="4">
-  <s>
-    <k n="_Self" t="i"/>
-  </s>
-  <s>
-    <k n="link" t="s"/>
-    <k n="logo" t="s"/>
-    <k n="name" t="s"/>
-  </s>
-  <s>
-    <k n="drw" t="i"/>
-    <k n="dcol" t="i"/>
-    <k n="name" t="s"/>
-    <k n="array" t="s"/>
-    <k n="headers" t="b"/>
-  </s>
-  <s>
-    <k n="ArrayCardInfo" t="spb"/>
-  </s>
-</spbStructures>
-</file>
-
-<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
-<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="1">
-    <x:dxf>
-      <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </x:dxf>
-  </dxfs>
-  <richStyles>
-    <rSty dxfid="0"/>
-  </richStyles>
-</richStyleSheet>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
-  <rel r:id="rId4"/>
-  <rel r:id="rId5"/>
-</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2763,6 +2097,7 @@
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="2" width="12.0703125" customWidth="1"/>
+    <col min="4" max="4" width="8.73828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.85">
@@ -3935,785 +3270,348 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D059EF-DBD7-449D-AE98-3E439228E9FA}">
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C196"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="18.92578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.73828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.8515625" customWidth="1"/>
+    <col min="5" max="5" width="8.73828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A1" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(0,0,passengers[#All])</f>
-        <v/>
-      </c>
-      <c r="B1" t="str">
-        <f ca="1"/>
-        <v>passengers</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A2" s="3" t="str">
-        <f ca="1"/>
-        <v>date</v>
-      </c>
-      <c r="B2" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A3" s="3" vm="2">
-        <f ca="1"/>
-        <v>17899</v>
-      </c>
-      <c r="B3">
-        <f ca="1"/>
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A4" s="3" vm="3">
-        <f ca="1"/>
-        <v>17930</v>
-      </c>
-      <c r="B4">
-        <f ca="1"/>
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A5" s="3" vm="4">
-        <f ca="1"/>
-        <v>17958</v>
-      </c>
-      <c r="B5">
-        <f ca="1"/>
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A6" s="3" vm="5">
-        <f ca="1"/>
-        <v>17989</v>
-      </c>
-      <c r="B6">
-        <f ca="1"/>
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A7" s="3" vm="6">
-        <f ca="1"/>
-        <v>18019</v>
-      </c>
-      <c r="B7">
-        <f ca="1"/>
-        <v>121</v>
+      <c r="A1" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A1">_xlfn._xlws.PY(0,0,passengers[#All])</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A9" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A9:B15" ca="1">_xlfn._xlws.PY(1,0)</f>
-        <v/>
-      </c>
-      <c r="B9" t="str">
-        <f ca="1"/>
-        <v>passengers</v>
+      <c r="A9" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A9">_xlfn._xlws.PY(1,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A10" s="3" t="str">
-        <f ca="1"/>
-        <v>date</v>
-      </c>
-      <c r="B10" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
+      <c r="B10" s="6"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A11" s="3" vm="7">
-        <f ca="1"/>
-        <v>17988</v>
-      </c>
-      <c r="B11">
-        <f ca="1"/>
-        <v>362</v>
-      </c>
+      <c r="B11" s="6"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A12" s="3" vm="8">
-        <f ca="1"/>
-        <v>18079</v>
-      </c>
-      <c r="B12">
-        <f ca="1"/>
-        <v>385</v>
-      </c>
+      <c r="B12" s="6"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A13" s="3" vm="9">
-        <f ca="1"/>
-        <v>18171</v>
-      </c>
-      <c r="B13">
-        <f ca="1"/>
-        <v>432</v>
-      </c>
+      <c r="B13" s="6"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A14" s="3" vm="10">
-        <f ca="1"/>
-        <v>18263</v>
-      </c>
-      <c r="B14">
-        <f ca="1"/>
-        <v>341</v>
-      </c>
+      <c r="B14" s="6"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A15" s="3" vm="11">
-        <f ca="1"/>
-        <v>18353</v>
-      </c>
-      <c r="B15">
-        <f ca="1"/>
-        <v>382</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A18" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A18:B33" ca="1">_xlfn._xlws.PY(2,0)</f>
-        <v>date</v>
-      </c>
-      <c r="B18" s="5" t="str">
-        <f ca="1"/>
-        <v>trend</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A19" s="3" vm="2">
-        <f ca="1"/>
-        <v>17899</v>
-      </c>
-      <c r="B19" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A20" s="3" vm="3">
-        <f ca="1"/>
-        <v>17930</v>
-      </c>
-      <c r="B20" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A21" s="3" vm="4">
-        <f ca="1"/>
-        <v>17958</v>
-      </c>
-      <c r="B21" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A22" s="3" vm="5">
-        <f ca="1"/>
-        <v>17989</v>
-      </c>
-      <c r="B22" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A23" s="3" vm="6">
-        <f ca="1"/>
-        <v>18019</v>
-      </c>
-      <c r="B23" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A24" s="3" vm="12">
-        <f ca="1"/>
-        <v>18050</v>
-      </c>
-      <c r="B24" s="5" t="e">
-        <f ca="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A25" s="3" vm="13">
-        <f ca="1"/>
-        <v>18080</v>
-      </c>
-      <c r="B25" s="5">
-        <f ca="1"/>
-        <v>126.79166666666666</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A26" s="3" vm="14">
-        <f ca="1"/>
-        <v>18111</v>
-      </c>
-      <c r="B26" s="5">
-        <f ca="1"/>
-        <v>127.24999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A27" s="3" vm="15">
-        <f ca="1"/>
-        <v>18142</v>
-      </c>
-      <c r="B27" s="5">
-        <f ca="1"/>
-        <v>127.95833333333331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A28" s="3" vm="16">
-        <f ca="1"/>
-        <v>18172</v>
-      </c>
-      <c r="B28" s="5">
-        <f ca="1"/>
-        <v>128.58333333333331</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A29" s="3" vm="17">
-        <f ca="1"/>
-        <v>18203</v>
-      </c>
-      <c r="B29" s="5">
-        <f ca="1"/>
-        <v>128.99999999999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A30" s="3" vm="18">
-        <f ca="1"/>
-        <v>18233</v>
-      </c>
-      <c r="B30" s="5">
-        <f ca="1"/>
-        <v>129.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A31" s="3" vm="19">
-        <f ca="1"/>
-        <v>18264</v>
-      </c>
-      <c r="B31" s="5">
-        <f ca="1"/>
-        <v>131.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A32" s="3" vm="20">
-        <f ca="1"/>
-        <v>18295</v>
-      </c>
-      <c r="B32" s="5">
-        <f ca="1"/>
-        <v>133.08333333333334</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A33" s="3" vm="21">
-        <f ca="1"/>
-        <v>18323</v>
-      </c>
-      <c r="B33" s="5">
-        <f ca="1"/>
-        <v>134.91666666666669</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A36" s="3" t="e" cm="1" vm="22">
-        <f t="array" aca="1" ref="A36" ca="1">_xlfn._xlws.PY(3,0)</f>
+      <c r="B15" s="6"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.85">
+      <c r="A17" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A17">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="B51" s="6"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A52" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A52:B62" ca="1">_xlfn._xlws.PY(4,0)</f>
-        <v>date</v>
-      </c>
-      <c r="B52" s="6" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A53" s="3" vm="2">
-        <f ca="1"/>
-        <v>17899</v>
-      </c>
-      <c r="B53" s="6">
-        <f ca="1"/>
-        <v>111.95999796199298</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A54" s="3" vm="3">
-        <f ca="1"/>
-        <v>17930</v>
-      </c>
-      <c r="B54" s="6">
-        <f ca="1"/>
-        <v>120.19333660189936</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A55" s="3" vm="4">
-        <f ca="1"/>
-        <v>17958</v>
-      </c>
-      <c r="B55" s="6">
-        <f ca="1"/>
-        <v>134.67683544691363</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A56" s="3" vm="5">
-        <f ca="1"/>
-        <v>17989</v>
-      </c>
-      <c r="B56" s="6">
-        <f ca="1"/>
-        <v>131.40726345798356</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A57" s="3" vm="6">
-        <f ca="1"/>
-        <v>18019</v>
-      </c>
-      <c r="B57" s="6">
-        <f ca="1"/>
-        <v>124.64374307768698</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A58" s="3" vm="12">
-        <f ca="1"/>
-        <v>18050</v>
-      </c>
-      <c r="B58" s="6">
-        <f ca="1"/>
-        <v>140.4272455247596</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A59" s="3" vm="13">
-        <f ca="1"/>
-        <v>18080</v>
-      </c>
-      <c r="B59" s="6">
-        <f ca="1"/>
-        <v>153.85808678698692</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A60" s="3" vm="14">
-        <f ca="1"/>
-        <v>18111</v>
-      </c>
-      <c r="B60" s="6">
-        <f ca="1"/>
-        <v>152.4364177143994</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A61" s="3" vm="15">
-        <f ca="1"/>
-        <v>18142</v>
-      </c>
-      <c r="B61" s="6">
-        <f ca="1"/>
-        <v>139.68358943158842</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A62" s="3" vm="16">
-        <f ca="1"/>
-        <v>18172</v>
-      </c>
-      <c r="B62" s="6">
-        <f ca="1"/>
-        <v>122.38855242329556</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A64" s="3" t="e" cm="1" vm="23">
-        <f t="array" aca="1" ref="A64" ca="1">_xlfn._xlws.PY(5,1)</f>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A44" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A44">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A68" s="3" t="e" cm="1" vm="24">
-        <f t="array" aca="1" ref="A68" ca="1">_xlfn._xlws.PY(6,0)</f>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C45" s="6"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C46" s="6"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C47" s="6"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C48" s="6"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C49" s="6"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C50" s="6"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C51" s="6"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C52" s="6"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C53" s="6"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C54" s="6"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C55" s="6"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C56" s="6"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C57" s="6"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="C58" s="6"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A60" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A60">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A70" s="3" t="e" cm="1" vm="25">
-        <f t="array" aca="1" ref="A70" ca="1">_xlfn._xlws.PY(7,0)</f>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A86" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A86">_xlfn._xlws.PY(5,0)</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A77" s="3" t="e" cm="1" vm="24">
-        <f t="array" aca="1" ref="A77" ca="1">_xlfn._xlws.PY(8,0)</f>
+      <c r="B86" s="5"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B87" s="5"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B88" s="5"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B89" s="5"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B90" s="5"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B91" s="5"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B92" s="5"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B93" s="5"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B94" s="5"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B95" s="5"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B96" s="5"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B97" s="5"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B98" s="5"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B99" s="5"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B100" s="5"/>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B101" s="5"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A104" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A104">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A85" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A85:B87" ca="1">_xlfn._xlws.PY(9,0)</f>
-        <v>Metric</v>
-      </c>
-      <c r="B85" t="str">
-        <f ca="1"/>
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A86" s="3" t="str">
-        <f ca="1"/>
-        <v>Test Statistic</v>
-      </c>
-      <c r="B86" s="6">
-        <f ca="1"/>
-        <v>0.81536887920606549</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A87" s="3" t="str">
-        <f ca="1"/>
-        <v>p-value</v>
-      </c>
-      <c r="B87" s="6">
-        <f ca="1"/>
-        <v>0.99188024343764125</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A89" s="3" t="e" cm="1" vm="26">
-        <f t="array" aca="1" ref="A89" ca="1">_xlfn._xlws.PY(10,1)</f>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B119" s="6"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A120" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A120">_xlfn._xlws.PY(7,0)</f>
         <v>#VALUE!</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A91" s="3" t="e" cm="1" vm="27">
-        <f t="array" aca="1" ref="A91" ca="1">_xlfn._xlws.PY(11,1)</f>
+      <c r="B120" s="6"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B121" s="6"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B122" s="6"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B123" s="6"/>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B124" s="6"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B125" s="6"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B126" s="6"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B127" s="6"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B128" s="6"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B129" s="6"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B130" s="6"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A132" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A132">_xlfn._xlws.PY(8,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A93" s="3" cm="1" vm="28">
-        <f t="array" aca="1" ref="A93:B97" ca="1">_xlfn._xlws.PY(12,0)</f>
-        <v>21551</v>
-      </c>
-      <c r="B93" s="6">
-        <f ca="1"/>
-        <v>354.17364147573602</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A94" s="3" vm="29">
-        <f ca="1"/>
-        <v>21582</v>
-      </c>
-      <c r="B94" s="6">
-        <f ca="1"/>
-        <v>337.57319653024558</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A95" s="3" vm="30">
-        <f ca="1"/>
-        <v>21610</v>
-      </c>
-      <c r="B95" s="6">
-        <f ca="1"/>
-        <v>387.7744448625624</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A96" s="3" vm="31">
-        <f ca="1"/>
-        <v>21641</v>
-      </c>
-      <c r="B96" s="6">
-        <f ca="1"/>
-        <v>379.77500904445122</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A97" s="3" vm="32">
-        <f ca="1"/>
-        <v>21671</v>
-      </c>
-      <c r="B97" s="6">
-        <f ca="1"/>
-        <v>397.21314537513348</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A100" s="3" t="str" cm="1" vm="33">
-        <f t="array" aca="1" ref="A100" ca="1">_xlfn._xlws.PY(13,1)</f>
-        <v>Mean Absolute Error: 31.07</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A103" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A103:C115" ca="1">_xlfn._xlws.PY(14,0)</f>
-        <v>Actual</v>
-      </c>
-      <c r="B103" s="6" t="str">
-        <f ca="1"/>
-        <v>Forecast</v>
-      </c>
-      <c r="C103" s="6" t="str">
-        <f ca="1"/>
-        <v>Error</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A104" s="3">
-        <f ca="1"/>
-        <v>360</v>
-      </c>
-      <c r="B104" s="6">
-        <f ca="1"/>
-        <v>354.17364147573602</v>
-      </c>
-      <c r="C104" s="6">
-        <f ca="1"/>
-        <v>5.8263585242639806</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A105" s="3">
-        <f ca="1"/>
-        <v>342</v>
-      </c>
-      <c r="B105" s="6">
-        <f ca="1"/>
-        <v>337.57319653024558</v>
-      </c>
-      <c r="C105" s="6">
-        <f ca="1"/>
-        <v>4.4268034697544181</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A106" s="3">
-        <f ca="1"/>
-        <v>406</v>
-      </c>
-      <c r="B106" s="6">
-        <f ca="1"/>
-        <v>387.7744448625624</v>
-      </c>
-      <c r="C106" s="6">
-        <f ca="1"/>
-        <v>18.225555137437595</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A107" s="3">
-        <f ca="1"/>
-        <v>396</v>
-      </c>
-      <c r="B107" s="6">
-        <f ca="1"/>
-        <v>379.77500904445122</v>
-      </c>
-      <c r="C107" s="6">
-        <f ca="1"/>
-        <v>16.224990955548776</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A108" s="3">
-        <f ca="1"/>
-        <v>420</v>
-      </c>
-      <c r="B108" s="6">
-        <f ca="1"/>
-        <v>397.21314537513348</v>
-      </c>
-      <c r="C108" s="6">
-        <f ca="1"/>
-        <v>22.786854624866521</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A109" s="3">
-        <f ca="1"/>
-        <v>472</v>
-      </c>
-      <c r="B109" s="6">
-        <f ca="1"/>
-        <v>468.87706028701018</v>
-      </c>
-      <c r="C109" s="6">
-        <f ca="1"/>
-        <v>3.1229397129898189</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A110" s="3">
-        <f ca="1"/>
-        <v>548</v>
-      </c>
-      <c r="B110" s="6">
-        <f ca="1"/>
-        <v>520.42527545650694</v>
-      </c>
-      <c r="C110" s="6">
-        <f ca="1"/>
-        <v>27.574724543493062</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A111" s="3">
-        <f ca="1"/>
-        <v>559</v>
-      </c>
-      <c r="B111" s="6">
-        <f ca="1"/>
-        <v>526.51011146486042</v>
-      </c>
-      <c r="C111" s="6">
-        <f ca="1"/>
-        <v>32.489888535139585</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A112" s="3">
-        <f ca="1"/>
-        <v>463</v>
-      </c>
-      <c r="B112" s="6">
-        <f ca="1"/>
-        <v>427.87427734740862</v>
-      </c>
-      <c r="C112" s="6">
-        <f ca="1"/>
-        <v>35.125722652591378</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A113" s="3">
-        <f ca="1"/>
-        <v>407</v>
-      </c>
-      <c r="B113" s="6">
-        <f ca="1"/>
-        <v>381.94210181918794</v>
-      </c>
-      <c r="C113" s="6">
-        <f ca="1"/>
-        <v>25.05789818081206</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A114" s="3">
-        <f ca="1"/>
-        <v>362</v>
-      </c>
-      <c r="B114" s="6">
-        <f ca="1"/>
-        <v>334.44886906567876</v>
-      </c>
-      <c r="C114" s="6">
-        <f ca="1"/>
-        <v>27.551130934321236</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A115" s="3">
-        <f ca="1"/>
-        <v>405</v>
-      </c>
-      <c r="B115" s="6">
-        <f ca="1"/>
-        <v>373.5830131238987</v>
-      </c>
-      <c r="C115" s="6">
-        <f ca="1"/>
-        <v>31.416986876101305</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A119" s="3" cm="1" vm="34">
-        <f t="array" aca="1" ref="A119" ca="1">_xlfn._xlws.PY(15,1)</f>
-        <v>115.25</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A122" s="3" t="str" cm="1">
-        <f t="array" aca="1" ref="A122:B125" ca="1">_xlfn._xlws.PY(16,0)</f>
-        <v>Metric</v>
-      </c>
-      <c r="B122" t="str">
-        <f ca="1"/>
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A123" s="3" t="str">
-        <f ca="1"/>
-        <v>Holt-Winters MAE</v>
-      </c>
-      <c r="B123">
-        <f ca="1"/>
-        <v>31.07</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A124" s="3" t="str">
-        <f ca="1"/>
-        <v>Baseline MAE</v>
-      </c>
-      <c r="B124">
-        <f ca="1"/>
-        <v>115.25</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A125" s="3" t="str">
-        <f ca="1"/>
-        <v>Improvement (%)</v>
-      </c>
-      <c r="B125">
-        <f ca="1"/>
-        <v>73.040000000000006</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.85">
-      <c r="A128" s="3" t="e" cm="1" vm="35">
-        <f t="array" aca="1" ref="A128" ca="1">_xlfn._xlws.PY(17,0)</f>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A136" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A136">_xlfn._xlws.PY(9,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A138" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A138">_xlfn._xlws.PY(10,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A145" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A145">_xlfn._xlws.PY(11,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A153" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A153">_xlfn._xlws.PY(12,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B154" s="6"/>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="B155" s="6"/>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A157" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A157">_xlfn._xlws.PY(13,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.85">
+      <c r="A159" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A159">_xlfn._xlws.PY(14,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A161" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A161">_xlfn._xlws.PY(15,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B161" s="6"/>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B162" s="6"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B163" s="6"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B164" s="6"/>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B165" s="6"/>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A168" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A168">_xlfn._xlws.PY(16,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A171" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A171">_xlfn._xlws.PY(17,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B171" s="6"/>
+      <c r="C171" s="6"/>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B172" s="6"/>
+      <c r="C172" s="6"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B173" s="6"/>
+      <c r="C173" s="6"/>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B174" s="6"/>
+      <c r="C174" s="6"/>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B175" s="6"/>
+      <c r="C175" s="6"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B177" s="6"/>
+      <c r="C177" s="6"/>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B178" s="6"/>
+      <c r="C178" s="6"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B179" s="6"/>
+      <c r="C179" s="6"/>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B180" s="6"/>
+      <c r="C180" s="6"/>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B181" s="6"/>
+      <c r="C181" s="6"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B182" s="6"/>
+      <c r="C182" s="6"/>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="B183" s="6"/>
+      <c r="C183" s="6"/>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A187" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A187">_xlfn._xlws.PY(18,1)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.85">
+      <c r="A190" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A190">_xlfn._xlws.PY(19,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.85">
+      <c r="A196" s="3" t="e" cm="1" vm="1">
+        <f t="array" ref="A196">_xlfn._xlws.PY(20,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -5260,91 +4158,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D36D00-A3A2-41DD-AB6F-6740B077CEDA}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="8.73828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A1" t="str" cm="1">
-        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(18,0,shampoo[#All])</f>
-        <v/>
-      </c>
-      <c r="B1" t="str">
-        <f ca="1"/>
-        <v>sales</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A2" t="str">
-        <f ca="1"/>
-        <v>date</v>
-      </c>
-      <c r="B2" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A3" vm="36">
-        <f ca="1"/>
-        <v>36526</v>
-      </c>
-      <c r="B3">
-        <f ca="1"/>
-        <v>266</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A4" vm="37">
-        <f ca="1"/>
-        <v>36557</v>
-      </c>
-      <c r="B4">
-        <f ca="1"/>
-        <v>145.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A5" vm="38">
-        <f ca="1"/>
-        <v>36586</v>
-      </c>
-      <c r="B5">
-        <f ca="1"/>
-        <v>183.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A6" vm="39">
-        <f ca="1"/>
-        <v>36617</v>
-      </c>
-      <c r="B6">
-        <f ca="1"/>
-        <v>119.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A7" vm="40">
-        <f ca="1"/>
-        <v>36647</v>
-      </c>
-      <c r="B7">
-        <f ca="1"/>
-        <v>180.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.85">
-      <c r="A10" t="e" cm="1" vm="41">
-        <f t="array" aca="1" ref="A10" ca="1">_xlfn._xlws.PY(19,0)</f>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.85">
+      <c r="A1" t="e" cm="1" vm="1">
+        <f t="array" ref="A1">_xlfn._xlws.PY(21,0,shampoo[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.85">
+      <c r="A10" t="e" cm="1" vm="1">
+        <f t="array" ref="A10">_xlfn._xlws.PY(22,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.85">
-      <c r="A24" t="e" cm="1" vm="42">
-        <f t="array" aca="1" ref="A24" ca="1">_xlfn._xlws.PY(20,0)</f>
+      <c r="A24" t="e" cm="1" vm="1">
+        <f t="array" ref="A24">_xlfn._xlws.PY(23,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/ch_07_forecasting_time_series/ch_07_solutions.xlsx
+++ b/ch_07_forecasting_time_series/ch_07_solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30021"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4507EEEF-B5AF-41C4-9ACE-1E3D2FCCA916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAA6EB7-5960-4F70-ADE3-D2A9828B33D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="2" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="147">
   <si>
     <t>1949-01</t>
   </si>
@@ -775,12 +775,6 @@
   </si>
   <si>
     <t>sales</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Sales</t>
   </si>
 </sst>
 </file>
@@ -2093,14 +2087,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30AC0CE-AC4D-4F0F-87BF-920A22749676}">
   <dimension ref="A1:B145"/>
-  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
-    <col min="2" max="2" width="12.0703125" customWidth="1"/>
-    <col min="4" max="4" width="8.73828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" customWidth="1"/>
+    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" s="1" t="s">
         <v>144</v>
       </c>
@@ -2108,7 +2102,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2116,7 +2110,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2124,7 +2118,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2132,7 +2126,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2140,7 +2134,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2148,7 +2142,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2156,7 +2150,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2164,7 +2158,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2172,7 +2166,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -2180,7 +2174,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2188,7 +2182,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -2196,7 +2190,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -2204,7 +2198,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -2212,7 +2206,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -2220,7 +2214,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -2228,7 +2222,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -2236,7 +2230,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -2244,7 +2238,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -2252,7 +2246,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -2260,7 +2254,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -2268,7 +2262,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -2276,7 +2270,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -2284,7 +2278,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -2292,7 +2286,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,7 +2294,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -2308,7 +2302,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -2316,7 +2310,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -2324,7 +2318,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -2332,7 +2326,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -2340,7 +2334,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -2348,7 +2342,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -2356,7 +2350,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -2364,7 +2358,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,7 +2366,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -2380,7 +2374,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -2388,7 +2382,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -2396,7 +2390,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -2404,7 +2398,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -2412,7 +2406,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -2420,7 +2414,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -2428,7 +2422,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -2436,7 +2430,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
@@ -2452,7 +2446,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -2460,7 +2454,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
@@ -2468,7 +2462,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -2476,7 +2470,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -2484,7 +2478,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
@@ -2492,7 +2486,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -2500,7 +2494,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -2508,7 +2502,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -2516,7 +2510,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -2524,7 +2518,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
@@ -2532,7 +2526,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
@@ -2540,7 +2534,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
@@ -2548,7 +2542,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
@@ -2556,7 +2550,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
@@ -2564,7 +2558,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -2572,7 +2566,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -2580,7 +2574,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,7 +2582,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -2596,7 +2590,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
@@ -2604,7 +2598,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
@@ -2612,7 +2606,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -2620,7 +2614,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
@@ -2628,7 +2622,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
@@ -2636,7 +2630,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
@@ -2644,7 +2638,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
@@ -2652,7 +2646,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
@@ -2660,7 +2654,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
@@ -2668,7 +2662,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
@@ -2676,7 +2670,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
@@ -2684,7 +2678,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
@@ -2692,7 +2686,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
@@ -2700,7 +2694,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
@@ -2708,7 +2702,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -2716,7 +2710,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
@@ -2724,7 +2718,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
@@ -2732,7 +2726,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
@@ -2740,7 +2734,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
@@ -2748,7 +2742,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
@@ -2756,7 +2750,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
@@ -2764,7 +2758,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
@@ -2772,7 +2766,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
@@ -2780,7 +2774,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
@@ -2788,7 +2782,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
@@ -2796,7 +2790,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
@@ -2804,7 +2798,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
@@ -2812,7 +2806,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
@@ -2820,7 +2814,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
@@ -2828,7 +2822,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
@@ -2836,7 +2830,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
@@ -2844,7 +2838,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -2852,7 +2846,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -2860,7 +2854,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
@@ -2868,7 +2862,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
@@ -2876,7 +2870,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
@@ -2884,7 +2878,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
@@ -2892,7 +2886,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
@@ -2900,7 +2894,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
@@ -2908,7 +2902,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
@@ -2916,7 +2910,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
@@ -2924,7 +2918,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
@@ -2932,7 +2926,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
@@ -2940,7 +2934,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
@@ -2948,7 +2942,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
@@ -2956,7 +2950,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
@@ -2964,7 +2958,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A109" s="1" t="s">
         <v>107</v>
       </c>
@@ -2972,7 +2966,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A110" s="1" t="s">
         <v>108</v>
       </c>
@@ -2980,7 +2974,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A111" s="1" t="s">
         <v>109</v>
       </c>
@@ -2988,7 +2982,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A112" s="1" t="s">
         <v>110</v>
       </c>
@@ -2996,7 +2990,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A113" s="1" t="s">
         <v>111</v>
       </c>
@@ -3004,7 +2998,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A114" s="1" t="s">
         <v>112</v>
       </c>
@@ -3012,7 +3006,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A115" s="1" t="s">
         <v>113</v>
       </c>
@@ -3020,7 +3014,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A116" s="1" t="s">
         <v>114</v>
       </c>
@@ -3028,7 +3022,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A117" s="1" t="s">
         <v>115</v>
       </c>
@@ -3036,7 +3030,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A118" s="1" t="s">
         <v>116</v>
       </c>
@@ -3044,7 +3038,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A119" s="1" t="s">
         <v>117</v>
       </c>
@@ -3052,7 +3046,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A120" s="1" t="s">
         <v>118</v>
       </c>
@@ -3060,7 +3054,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A121" s="1" t="s">
         <v>119</v>
       </c>
@@ -3068,7 +3062,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A122" s="1" t="s">
         <v>120</v>
       </c>
@@ -3076,7 +3070,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A123" s="1" t="s">
         <v>121</v>
       </c>
@@ -3084,7 +3078,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A124" s="1" t="s">
         <v>122</v>
       </c>
@@ -3092,7 +3086,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A125" s="1" t="s">
         <v>123</v>
       </c>
@@ -3100,7 +3094,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A126" s="1" t="s">
         <v>124</v>
       </c>
@@ -3108,7 +3102,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A127" s="1" t="s">
         <v>125</v>
       </c>
@@ -3116,7 +3110,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A128" s="1" t="s">
         <v>126</v>
       </c>
@@ -3124,7 +3118,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A129" s="1" t="s">
         <v>127</v>
       </c>
@@ -3132,7 +3126,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A130" s="1" t="s">
         <v>128</v>
       </c>
@@ -3140,7 +3134,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A131" s="1" t="s">
         <v>129</v>
       </c>
@@ -3148,7 +3142,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A132" s="1" t="s">
         <v>130</v>
       </c>
@@ -3156,7 +3150,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A133" s="1" t="s">
         <v>131</v>
       </c>
@@ -3164,7 +3158,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A134" s="1" t="s">
         <v>132</v>
       </c>
@@ -3172,7 +3166,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A135" s="1" t="s">
         <v>133</v>
       </c>
@@ -3180,7 +3174,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A136" s="1" t="s">
         <v>134</v>
       </c>
@@ -3188,7 +3182,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A137" s="1" t="s">
         <v>135</v>
       </c>
@@ -3196,7 +3190,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A138" s="1" t="s">
         <v>136</v>
       </c>
@@ -3204,7 +3198,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -3212,7 +3206,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A140" s="1" t="s">
         <v>138</v>
       </c>
@@ -3220,7 +3214,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A141" s="1" t="s">
         <v>139</v>
       </c>
@@ -3228,7 +3222,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A142" s="1" t="s">
         <v>140</v>
       </c>
@@ -3236,7 +3230,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A143" s="1" t="s">
         <v>141</v>
       </c>
@@ -3244,7 +3238,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A144" s="1" t="s">
         <v>142</v>
       </c>
@@ -3252,7 +3246,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A145" s="1" t="s">
         <v>143</v>
       </c>
@@ -3271,277 +3265,277 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D059EF-DBD7-449D-AE98-3E439228E9FA}">
   <dimension ref="A1:C196"/>
-  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="18.92578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.73828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.8515625" customWidth="1"/>
-    <col min="5" max="5" width="8.73828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.9140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A1">_xlfn._xlws.PY(0,0,passengers[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A9" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A9">_xlfn._xlws.PY(1,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B10" s="6"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B11" s="6"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B12" s="6"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B13" s="6"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B14" s="6"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B15" s="6"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.85">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.7">
       <c r="A17" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A17">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A44" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A44">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="C44" s="6"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C45" s="6"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C46" s="6"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C47" s="6"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C48" s="6"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C49" s="6"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C50" s="6"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C51" s="6"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C52" s="6"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C53" s="6"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C54" s="6"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C55" s="6"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C56" s="6"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C57" s="6"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C58" s="6"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A60" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A60">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A86" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A86">_xlfn._xlws.PY(5,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B86" s="5"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B87" s="5"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B88" s="5"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B89" s="5"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B90" s="5"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B91" s="5"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B92" s="5"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B93" s="5"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B94" s="5"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B95" s="5"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B96" s="5"/>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B97" s="5"/>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B98" s="5"/>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B99" s="5"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B100" s="5"/>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B101" s="5"/>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A104" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A104">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B119" s="6"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A120" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A120">_xlfn._xlws.PY(7,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B120" s="6"/>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B121" s="6"/>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B122" s="6"/>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B123" s="6"/>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B124" s="6"/>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B125" s="6"/>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B126" s="6"/>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B127" s="6"/>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B128" s="6"/>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B129" s="6"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B130" s="6"/>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A132" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A132">_xlfn._xlws.PY(8,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A136" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A136">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A138" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A138">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A145" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A145">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A153" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A153">_xlfn._xlws.PY(12,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B154" s="6"/>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.7">
       <c r="B155" s="6"/>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A157" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A157">_xlfn._xlws.PY(13,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.85">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A159" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A159">_xlfn._xlws.PY(14,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A161" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A161">_xlfn._xlws.PY(15,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B161" s="6"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B162" s="6"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B163" s="6"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B164" s="6"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B165" s="6"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A168" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A168">_xlfn._xlws.PY(16,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A171" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A171">_xlfn._xlws.PY(17,0)</f>
         <v>#VALUE!</v>
@@ -3549,67 +3543,67 @@
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A187" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A187">_xlfn._xlws.PY(18,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.85">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A190" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A190">_xlfn._xlws.PY(19,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.85">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.7">
       <c r="A196" s="3" t="e" cm="1" vm="1">
         <f t="array" ref="A196">_xlfn._xlws.PY(20,0)</f>
         <v>#VALUE!</v>
@@ -3624,529 +3618,343 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF831C9-C517-44BA-811F-F102BEB016DE}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B1" t="s">
         <v>146</v>
       </c>
-      <c r="F1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.85">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A2" s="2">
         <v>36526</v>
       </c>
       <c r="B2">
         <v>266</v>
       </c>
-      <c r="F2" s="4">
-        <v>46023</v>
-      </c>
-      <c r="G2">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A3" s="2">
         <v>36557</v>
       </c>
       <c r="B3">
         <v>145.9</v>
       </c>
-      <c r="F3" s="4">
-        <v>46024</v>
-      </c>
-      <c r="G3">
-        <v>145.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A4" s="2">
         <v>36586</v>
       </c>
       <c r="B4">
         <v>183.1</v>
       </c>
-      <c r="F4" s="4">
-        <v>46025</v>
-      </c>
-      <c r="G4">
-        <v>183.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A5" s="2">
         <v>36617</v>
       </c>
       <c r="B5">
         <v>119.3</v>
       </c>
-      <c r="F5" s="4">
-        <v>46026</v>
-      </c>
-      <c r="G5">
-        <v>119.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A6" s="2">
         <v>36647</v>
       </c>
       <c r="B6">
         <v>180.3</v>
       </c>
-      <c r="F6" s="4">
-        <v>46027</v>
-      </c>
-      <c r="G6">
-        <v>180.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A7" s="2">
         <v>36678</v>
       </c>
       <c r="B7">
         <v>168.5</v>
       </c>
-      <c r="F7" s="4">
-        <v>46028</v>
-      </c>
-      <c r="G7">
-        <v>168.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A8" s="2">
         <v>36708</v>
       </c>
       <c r="B8">
         <v>231.8</v>
       </c>
-      <c r="F8" s="4">
-        <v>46029</v>
-      </c>
-      <c r="G8">
-        <v>231.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A9" s="2">
         <v>36739</v>
       </c>
       <c r="B9">
         <v>224.5</v>
       </c>
-      <c r="F9" s="4">
-        <v>46030</v>
-      </c>
-      <c r="G9">
-        <v>224.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A10" s="2">
         <v>36770</v>
       </c>
       <c r="B10">
         <v>192.8</v>
       </c>
-      <c r="F10" s="4">
-        <v>46031</v>
-      </c>
-      <c r="G10">
-        <v>192.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A11" s="2">
         <v>36800</v>
       </c>
       <c r="B11">
         <v>122.9</v>
       </c>
-      <c r="F11" s="4">
-        <v>46032</v>
-      </c>
-      <c r="G11">
-        <v>122.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A12" s="2">
         <v>36831</v>
       </c>
       <c r="B12">
         <v>336.5</v>
       </c>
-      <c r="F12" s="4">
-        <v>46033</v>
-      </c>
-      <c r="G12">
-        <v>336.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A13" s="2">
         <v>36861</v>
       </c>
       <c r="B13">
         <v>185.9</v>
       </c>
-      <c r="F13" s="4">
-        <v>46034</v>
-      </c>
-      <c r="G13">
-        <v>185.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A14" s="2">
         <v>36892</v>
       </c>
       <c r="B14">
         <v>194.3</v>
       </c>
-      <c r="F14" s="4">
-        <v>46054</v>
-      </c>
-      <c r="G14">
-        <v>194.3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A15" s="2">
         <v>36923</v>
       </c>
       <c r="B15">
         <v>149.5</v>
       </c>
-      <c r="F15" s="4">
-        <v>46055</v>
-      </c>
-      <c r="G15">
-        <v>149.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A16" s="2">
         <v>36951</v>
       </c>
       <c r="B16">
         <v>210.1</v>
       </c>
-      <c r="F16" s="4">
-        <v>46056</v>
-      </c>
-      <c r="G16">
-        <v>210.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A17" s="2">
         <v>36982</v>
       </c>
       <c r="B17">
         <v>273.3</v>
       </c>
-      <c r="F17" s="4">
-        <v>46057</v>
-      </c>
-      <c r="G17">
-        <v>273.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A18" s="2">
         <v>37012</v>
       </c>
       <c r="B18">
         <v>191.4</v>
       </c>
-      <c r="F18" s="4">
-        <v>46058</v>
-      </c>
-      <c r="G18">
-        <v>191.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A19" s="2">
         <v>37043</v>
       </c>
       <c r="B19">
         <v>287</v>
       </c>
-      <c r="F19" s="4">
-        <v>46059</v>
-      </c>
-      <c r="G19">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A20" s="2">
         <v>37073</v>
       </c>
       <c r="B20">
         <v>226</v>
       </c>
-      <c r="F20" s="4">
-        <v>46060</v>
-      </c>
-      <c r="G20">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A21" s="2">
         <v>37104</v>
       </c>
       <c r="B21">
         <v>303.60000000000002</v>
       </c>
-      <c r="F21" s="4">
-        <v>46061</v>
-      </c>
-      <c r="G21">
-        <v>303.60000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A22" s="2">
         <v>37135</v>
       </c>
       <c r="B22">
         <v>289.89999999999998</v>
       </c>
-      <c r="F22" s="4">
-        <v>46062</v>
-      </c>
-      <c r="G22">
-        <v>289.89999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A23" s="2">
         <v>37165</v>
       </c>
       <c r="B23">
         <v>421.6</v>
       </c>
-      <c r="F23" s="4">
-        <v>46063</v>
-      </c>
-      <c r="G23">
-        <v>421.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A24" s="2">
         <v>37196</v>
       </c>
       <c r="B24">
         <v>264.5</v>
       </c>
-      <c r="F24" s="4">
-        <v>46064</v>
-      </c>
-      <c r="G24">
-        <v>264.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A25" s="2">
         <v>37226</v>
       </c>
       <c r="B25">
         <v>342.3</v>
       </c>
-      <c r="F25" s="4">
-        <v>46065</v>
-      </c>
-      <c r="G25">
-        <v>342.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A26" s="2">
         <v>37257</v>
       </c>
       <c r="B26">
         <v>339.7</v>
       </c>
-      <c r="F26" s="4">
-        <v>46082</v>
-      </c>
-      <c r="G26">
-        <v>339.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A27" s="2">
         <v>37288</v>
       </c>
       <c r="B27">
         <v>440.4</v>
       </c>
-      <c r="F27" s="4">
-        <v>46083</v>
-      </c>
-      <c r="G27">
-        <v>440.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A28" s="2">
         <v>37316</v>
       </c>
       <c r="B28">
         <v>315.89999999999998</v>
       </c>
-      <c r="F28" s="4">
-        <v>46084</v>
-      </c>
-      <c r="G28">
-        <v>315.89999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A29" s="2">
         <v>37347</v>
       </c>
       <c r="B29">
         <v>439.3</v>
       </c>
-      <c r="F29" s="4">
-        <v>46085</v>
-      </c>
-      <c r="G29">
-        <v>439.3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A30" s="2">
         <v>37377</v>
       </c>
       <c r="B30">
         <v>401.3</v>
       </c>
-      <c r="F30" s="4">
-        <v>46086</v>
-      </c>
-      <c r="G30">
-        <v>401.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A31" s="2">
         <v>37408</v>
       </c>
       <c r="B31">
         <v>437.4</v>
       </c>
-      <c r="F31" s="4">
-        <v>46087</v>
-      </c>
-      <c r="G31">
-        <v>437.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A32" s="2">
         <v>37438</v>
       </c>
       <c r="B32">
         <v>575.5</v>
       </c>
-      <c r="F32" s="4">
-        <v>46088</v>
-      </c>
-      <c r="G32">
-        <v>575.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A33" s="2">
         <v>37469</v>
       </c>
       <c r="B33">
         <v>407.6</v>
       </c>
-      <c r="F33" s="4">
-        <v>46089</v>
-      </c>
-      <c r="G33">
-        <v>407.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A34" s="2">
         <v>37500</v>
       </c>
       <c r="B34">
         <v>682</v>
       </c>
-      <c r="F34" s="4">
-        <v>46090</v>
-      </c>
-      <c r="G34">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A35" s="2">
         <v>37530</v>
       </c>
       <c r="B35">
         <v>475.3</v>
       </c>
-      <c r="F35" s="4">
-        <v>46091</v>
-      </c>
-      <c r="G35">
-        <v>475.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A36" s="2">
         <v>37561</v>
       </c>
       <c r="B36">
         <v>581.29999999999995</v>
       </c>
-      <c r="F36" s="4">
-        <v>46092</v>
-      </c>
-      <c r="G36">
-        <v>581.29999999999995</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.85">
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.7">
       <c r="A37" s="2">
         <v>37591</v>
       </c>
       <c r="B37">
         <v>646.9</v>
       </c>
-      <c r="F37" s="4">
-        <v>46093</v>
-      </c>
-      <c r="G37">
-        <v>646.9</v>
-      </c>
+      <c r="F37" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4159,24 +3967,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D36D00-A3A2-41DD-AB6F-6740B077CEDA}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.85"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="8.73828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.7">
       <c r="A1" t="e" cm="1" vm="1">
         <f t="array" ref="A1">_xlfn._xlws.PY(21,0,shampoo[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.85">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.7">
       <c r="A10" t="e" cm="1" vm="1">
         <f t="array" ref="A10">_xlfn._xlws.PY(22,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.85">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.7">
       <c r="A24" t="e" cm="1" vm="1">
         <f t="array" ref="A24">_xlfn._xlws.PY(23,0)</f>
         <v>#VALUE!</v>

--- a/ch_07_forecasting_time_series/ch_07_solutions.xlsx
+++ b/ch_07_forecasting_time_series/ch_07_solutions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAA6EB7-5960-4F70-ADE3-D2A9828B33D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B81526-F8A4-4EAD-B418-4B548E2947B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="2" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" firstSheet="1" activeTab="3" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
+  <futureMetadata name="XLRICHVALUE" count="44">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -58,15 +58,445 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="15"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="17"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="18"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="20"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="21"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="22"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="23"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="24"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="25"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="39"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="40"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="27"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="28"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="30"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="31"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="41"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="42"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="43"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="44"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="45"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="46"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="47"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="48"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="49"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="50"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
+  <valueMetadata count="44">
     <bk>
       <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
+    </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
+    <bk>
+      <rc t="2" v="7"/>
+    </bk>
+    <bk>
+      <rc t="2" v="8"/>
+    </bk>
+    <bk>
+      <rc t="2" v="9"/>
+    </bk>
+    <bk>
+      <rc t="2" v="10"/>
+    </bk>
+    <bk>
+      <rc t="2" v="11"/>
+    </bk>
+    <bk>
+      <rc t="2" v="12"/>
+    </bk>
+    <bk>
+      <rc t="2" v="13"/>
+    </bk>
+    <bk>
+      <rc t="2" v="14"/>
+    </bk>
+    <bk>
+      <rc t="2" v="15"/>
+    </bk>
+    <bk>
+      <rc t="2" v="16"/>
+    </bk>
+    <bk>
+      <rc t="2" v="17"/>
+    </bk>
+    <bk>
+      <rc t="2" v="18"/>
+    </bk>
+    <bk>
+      <rc t="2" v="19"/>
+    </bk>
+    <bk>
+      <rc t="2" v="20"/>
+    </bk>
+    <bk>
+      <rc t="2" v="21"/>
+    </bk>
+    <bk>
+      <rc t="2" v="22"/>
+    </bk>
+    <bk>
+      <rc t="2" v="23"/>
+    </bk>
+    <bk>
+      <rc t="2" v="24"/>
+    </bk>
+    <bk>
+      <rc t="2" v="25"/>
+    </bk>
+    <bk>
+      <rc t="2" v="26"/>
+    </bk>
+    <bk>
+      <rc t="2" v="27"/>
+    </bk>
+    <bk>
+      <rc t="2" v="28"/>
+    </bk>
+    <bk>
+      <rc t="2" v="29"/>
+    </bk>
+    <bk>
+      <rc t="2" v="30"/>
+    </bk>
+    <bk>
+      <rc t="2" v="31"/>
+    </bk>
+    <bk>
+      <rc t="2" v="32"/>
+    </bk>
+    <bk>
+      <rc t="2" v="33"/>
+    </bk>
+    <bk>
+      <rc t="2" v="34"/>
+    </bk>
+    <bk>
+      <rc t="2" v="35"/>
+    </bk>
+    <bk>
+      <rc t="2" v="36"/>
+    </bk>
+    <bk>
+      <rc t="2" v="37"/>
+    </bk>
+    <bk>
+      <rc t="2" v="38"/>
+    </bk>
+    <bk>
+      <rc t="2" v="39"/>
+    </bk>
+    <bk>
+      <rc t="2" v="40"/>
+    </bk>
+    <bk>
+      <rc t="2" v="41"/>
+    </bk>
+    <bk>
+      <rc t="2" v="42"/>
+    </bk>
+    <bk>
+      <rc t="2" v="43"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -75,7 +505,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -296,32 +726,17 @@
 shampoo_df.head()</code>
     </pythonScript>
     <pythonScript>
-      <code xml:space="preserve"># Create side-by-side subplots 
-fig, axes = plt.subplots(nrows=1, ncols=2, figsize=(12, 4)) 
-# Plot airline passengers 
-sns.lineplot( 
-x=passengers_df.index, 
-y=passengers_df['passengers'], 
-linewidth=2, 
-ax=axes[0] 
-) 
+      <code xml:space="preserve">fig, axes = plt.subplots(2, 1, figsize=(12, 4)) 
+sns.lineplot(x=passengers_df.index, y=passengers_df['passengers'], 
+linewidth=2, ax=axes[0]) 
 axes[0].set_title('Airline Passengers') 
 axes[0].set_ylabel('Count') 
 axes[0].grid(True, alpha=0.3) 
-# Plot shampoo sales 
-sns.lineplot( 
-x=shampoo_df.index, 
-y=shampoo_df['sales'], 
-color='green', 
-linewidth=2, 
-ax=axes[1] 
-) 
+sns.lineplot(x=shampoo_df.index, y=shampoo_df['sales'], color='green', linewidth=2, ax=axes[1]) 
 axes[1].set_title('Shampoo Sales') 
 axes[1].set_ylabel('Sales') 
 axes[1].grid(True, alpha=0.3) 
-# Adjust layout 
-plt.tight_layout() 
- </code>
+plt.tight_layout() </code>
     </pythonScript>
     <pythonScript>
       <code>shampoo_decomp = seasonal_decompose(shampoo_df['sales'], model='additive', period=12)
@@ -1318,10 +1733,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1592,13 +2007,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>795867</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>8467</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>637721</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>84676</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1614,7 +2029,7 @@
           <a:picLocks noChangeAspect="1"/>
           <a:extLst>
             <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A24"/>
+              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="shampoo_ts!A27"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPicPr>
@@ -1641,21 +2056,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>53982</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>228889</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>914993</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>89542</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="Image generated by Python">
+        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FD7E82C-8FB0-598D-7934-A5F67574A01E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A7623B7E-9C34-965A-5338-19780AF2937A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1676,8 +2091,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="2730500"/>
-          <a:ext cx="10863094" cy="3566167"/>
+          <a:off x="0" y="3278188"/>
+          <a:ext cx="10844806" cy="3566167"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1729,29 +2144,428 @@
 </rvTypesInfo>
 </file>
 
+<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
+  <a r="13" c="3">
+    <v t="s"/>
+    <v t="s">passengers</v>
+    <v t="s">rolling_mean</v>
+    <v t="s">date</v>
+    <v t="s"/>
+    <v t="s"/>
+    <v t="r">27</v>
+    <v>360</v>
+    <v>382.66666666666669</v>
+    <v t="r">28</v>
+    <v>342</v>
+    <v>384.66666666666669</v>
+    <v t="r">29</v>
+    <v>406</v>
+    <v>388.33333333333331</v>
+    <v t="r">30</v>
+    <v>396</v>
+    <v>392.33333333333331</v>
+    <v t="r">31</v>
+    <v>420</v>
+    <v>397.08333333333331</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="r">32</v>
+    <v>606</v>
+    <v>463.33333333333331</v>
+    <v t="r">33</v>
+    <v>508</v>
+    <v>467.08333333333331</v>
+    <v t="r">34</v>
+    <v>461</v>
+    <v>471.58333333333331</v>
+    <v t="r">35</v>
+    <v>390</v>
+    <v>473.91666666666669</v>
+    <v t="r">36</v>
+    <v>432</v>
+    <v>476.16666666666669</v>
+  </a>
+</arrayData>
+</file>
+
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="51">
   <rv s="0">
+    <fb>17899</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>17930</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>17958</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>17989</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18019</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>17988</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18079</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18171</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18263</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18353</fb>
+    <v>0</v>
+  </rv>
+  <rv s="1">
+    <v>0</v>
     <v>9</v>
-    <v>18</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="0">
+    <fb>18050</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18080</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18111</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18142</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18172</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18203</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18233</fb>
+    <v>0</v>
+  </rv>
+  <rv s="1">
+    <v>1</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="0">
+    <fb>18264</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18295</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>18323</fb>
+    <v>0</v>
+  </rv>
+  <rv s="1">
+    <v>2</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="2">
+    <v>&lt;class 'pandas.core.indexes.datetimes.DatetimeIndex'&gt;</v>
+    <v>DatetimeIndex</v>
+    <v>DatetimeIndex(['1961-01-01', '1961-02-01', '1961-03-01', '1961-04-01',
+               '1961-05-01', '1961-06-01', '1961-07-01', '1961-08-01',
+               '1961-09-01', '1961-10-01', '1961-11-01', '1961-12-01',
+               '1962-01-01', '1962-02-0...</v>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <v>3</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="3">
+    <v>0</v>
+    <v>8</v>
+    <v>23</v>
+    <v>1</v>
+  </rv>
+  <rv s="4">
+    <v>14</v>
+  </rv>
+  <rv s="0">
+    <fb>21551</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>21582</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>21610</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>21641</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>21671</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22129</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22160</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22190</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22221</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>22251</fb>
+    <v>0</v>
+  </rv>
+  <rv s="5">
+    <v>0</v>
+  </rv>
+  <rv s="6">
+    <v>DataFrame</v>
+    <v>3</v>
+    <v>37</v>
+  </rv>
+  <rv s="7">
+    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
+    <v>DataFrame</v>
+    <v xml:space="preserve">            passengers  rolling_mean
+date                                
+1959-01-01         360    382.666667
+1959-02-01         342    384.666667
+1959-03-01         406    388.333333
+1959-04-01         396    392.333333
+1959-05-01         420    397....</v>
+    <v>38</v>
+    <v>1</v>
+  </rv>
+  <rv s="2">
+    <v>&lt;class 'statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper'&gt;</v>
+    <v>HoltWintersResultsWrapper</v>
+    <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f63d8a76900&gt;</v>
+    <v>1</v>
+  </rv>
+  <rv s="8">
+    <fb t="s">Mean Absolute Error: 31.07</fb>
+    <v>&lt;class 'str'&gt;</v>
+    <v>str</v>
+    <v>Mean Absolute Error: 31.07</v>
+    <v>Mean Absolute Error: 31.07</v>
+    <v>1</v>
+  </rv>
+  <rv s="9">
+    <fb>115.25</fb>
+    <v>&lt;class 'numpy.float64'&gt;</v>
+    <v>float64</v>
+    <v>115.25</v>
+    <v>115.25</v>
+    <v>1</v>
+  </rv>
+  <rv s="1">
+    <v>4</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="0">
+    <fb>36526</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>36557</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>36586</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>36617</fb>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb>36647</fb>
+    <v>0</v>
+  </rv>
+  <rv s="1">
+    <v>5</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
+  </rv>
+  <rv s="1">
+    <v>6</v>
+    <v>9</v>
+    <v>Image generated by Python</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+  <s t="_formattednumber">
+    <k n="_Format" t="spb"/>
+  </s>
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+    <k n="Text" t="s"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
   <s t="_error">
     <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
+  </s>
+  <s t="_array">
+    <k n="array" t="a"/>
+  </s>
+  <s t="_entity">
+    <k n="_DisplayString" t="s"/>
+    <k n="_ViewInfo" t="spb"/>
+    <k n="arrayPreview" t="r"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="preview" t="r"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="basicValue" t="s"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="basicValue"/>
+    <k n="_Provider" t="spb"/>
   </s>
 </rvStructures>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
+<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+  <spbData count="4">
+    <spb s="0">
+      <v>1</v>
+    </spb>
+    <spb s="1">
+      <v>https://www.anaconda.com/excel</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
+      <v>Python provided by Anaconda</v>
+    </spb>
+    <spb s="2">
+      <v>24</v>
+      <v>2</v>
+      <v>DataFrame</v>
+      <v>arrayPreview</v>
+      <v>1</v>
+    </spb>
+    <spb s="3">
+      <v>2</v>
+    </spb>
+  </spbData>
+</supportingPropertyBags>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="4">
+  <s>
+    <k n="_Self" t="i"/>
+  </s>
+  <s>
+    <k n="link" t="s"/>
+    <k n="logo" t="s"/>
+    <k n="name" t="s"/>
+  </s>
+  <s>
+    <k n="drw" t="i"/>
+    <k n="dcol" t="i"/>
+    <k n="name" t="s"/>
+    <k n="array" t="s"/>
+    <k n="headers" t="b"/>
+  </s>
+  <s>
+    <k n="ArrayCardInfo" t="spb"/>
+  </s>
+</spbStructures>
+</file>
+
+<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
+<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <dxfs count="1">
+    <x:dxf>
+      <x:numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </x:dxf>
+  </dxfs>
+  <richStyles>
+    <rSty dxfid="0"/>
+  </richStyles>
+</richStyleSheet>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+</richValueRels>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FEE9AA1-77C4-44CB-80EC-CCEE1A5E4B85}" name="passengers" displayName="passengers" ref="A1:B145" totalsRowShown="0">
   <autoFilter ref="A1:B145" xr:uid="{7FEE9AA1-77C4-44CB-80EC-CCEE1A5E4B85}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{89C61804-E37F-46DC-843D-09FC2BF32AF1}" name="date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{89C61804-E37F-46DC-843D-09FC2BF32AF1}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{D51D0BEF-BFC7-4F34-B98C-315FEBBB8A48}" name="passengers"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1762,7 +2576,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8070347D-7673-46D1-8207-A1D784ACEE59}" name="shampoo" displayName="shampoo" ref="A1:B37" totalsRowShown="0">
   <autoFilter ref="A1:B37" xr:uid="{8070347D-7673-46D1-8207-A1D784ACEE59}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4511BAD2-C5B8-4115-8ECF-666BFDD2B720}" name="date" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{4511BAD2-C5B8-4115-8ECF-666BFDD2B720}" name="date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{1B629950-5F4A-4F2E-B795-D39EC6984B40}" name="sales"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3274,338 +4088,913 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A1" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A1">_xlfn._xlws.PY(0,0,passengers[#All])</f>
-        <v>#VALUE!</v>
+      <c r="A1" s="3" t="str" cm="1">
+        <f t="array" ref="A1:B7">_xlfn._xlws.PY(0,0,passengers[#All])</f>
+        <v/>
+      </c>
+      <c r="B1" t="str">
+        <v>passengers</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A2" s="3" t="str">
+        <v>date</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A3" s="3" vm="1">
+        <v>17899</v>
+      </c>
+      <c r="B3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A4" s="3" vm="2">
+        <v>17930</v>
+      </c>
+      <c r="B4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A5" s="3" vm="3">
+        <v>17958</v>
+      </c>
+      <c r="B5">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A6" s="3" vm="4">
+        <v>17989</v>
+      </c>
+      <c r="B6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A7" s="3" vm="5">
+        <v>18019</v>
+      </c>
+      <c r="B7">
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A9" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A9">_xlfn._xlws.PY(1,0)</f>
-        <v>#VALUE!</v>
+      <c r="A9" s="3" t="str" cm="1">
+        <f t="array" ref="A9:B15">_xlfn._xlws.PY(1,0)</f>
+        <v/>
+      </c>
+      <c r="B9" t="str">
+        <v>passengers</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B10" s="6"/>
+      <c r="A10" s="3" t="str">
+        <v>date</v>
+      </c>
+      <c r="B10" s="6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B11" s="6"/>
+      <c r="A11" s="3" vm="6">
+        <v>17988</v>
+      </c>
+      <c r="B11" s="6">
+        <v>120.66666666666667</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B12" s="6"/>
+      <c r="A12" s="3" vm="7">
+        <v>18079</v>
+      </c>
+      <c r="B12" s="6">
+        <v>128.33333333333334</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B13" s="6"/>
+      <c r="A13" s="3" vm="8">
+        <v>18171</v>
+      </c>
+      <c r="B13" s="6">
+        <v>144</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B14" s="6"/>
+      <c r="A14" s="3" vm="9">
+        <v>18263</v>
+      </c>
+      <c r="B14" s="6">
+        <v>113.66666666666667</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B15" s="6"/>
+      <c r="A15" s="3" vm="10">
+        <v>18353</v>
+      </c>
+      <c r="B15" s="6">
+        <v>127.33333333333333</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.7">
-      <c r="A17" s="3" t="e" cm="1" vm="1">
+      <c r="A17" s="3" t="e" cm="1" vm="11">
         <f t="array" ref="A17">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A44" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A44">_xlfn._xlws.PY(3,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C44" s="6"/>
+      <c r="A44" s="3" t="str" cm="1">
+        <f t="array" ref="A44:C57">_xlfn._xlws.PY(3,0)</f>
+        <v/>
+      </c>
+      <c r="B44" t="str">
+        <v>passengers</v>
+      </c>
+      <c r="C44" s="6" t="str">
+        <v>rolling_mean</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C45" s="6"/>
+      <c r="A45" s="3" t="str">
+        <v>date</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" s="6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C46" s="6"/>
+      <c r="A46" s="3" vm="1">
+        <v>17899</v>
+      </c>
+      <c r="B46">
+        <v>112</v>
+      </c>
+      <c r="C46" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C47" s="6"/>
+      <c r="A47" s="3" vm="2">
+        <v>17930</v>
+      </c>
+      <c r="B47">
+        <v>118</v>
+      </c>
+      <c r="C47" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C48" s="6"/>
+      <c r="A48" s="3" vm="3">
+        <v>17958</v>
+      </c>
+      <c r="B48">
+        <v>132</v>
+      </c>
+      <c r="C48" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C49" s="6"/>
+      <c r="A49" s="3" vm="4">
+        <v>17989</v>
+      </c>
+      <c r="B49">
+        <v>129</v>
+      </c>
+      <c r="C49" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C50" s="6"/>
+      <c r="A50" s="3" vm="5">
+        <v>18019</v>
+      </c>
+      <c r="B50">
+        <v>121</v>
+      </c>
+      <c r="C50" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C51" s="6"/>
+      <c r="A51" s="3" vm="12">
+        <v>18050</v>
+      </c>
+      <c r="B51">
+        <v>135</v>
+      </c>
+      <c r="C51" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C52" s="6"/>
+      <c r="A52" s="3" vm="13">
+        <v>18080</v>
+      </c>
+      <c r="B52">
+        <v>148</v>
+      </c>
+      <c r="C52" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C53" s="6"/>
+      <c r="A53" s="3" vm="14">
+        <v>18111</v>
+      </c>
+      <c r="B53">
+        <v>148</v>
+      </c>
+      <c r="C53" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C54" s="6"/>
+      <c r="A54" s="3" vm="15">
+        <v>18142</v>
+      </c>
+      <c r="B54">
+        <v>136</v>
+      </c>
+      <c r="C54" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C55" s="6"/>
+      <c r="A55" s="3" vm="16">
+        <v>18172</v>
+      </c>
+      <c r="B55">
+        <v>119</v>
+      </c>
+      <c r="C55" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C56" s="6"/>
+      <c r="A56" s="3" vm="17">
+        <v>18203</v>
+      </c>
+      <c r="B56">
+        <v>104</v>
+      </c>
+      <c r="C56" s="6" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="C57" s="6"/>
+      <c r="A57" s="3" vm="18">
+        <v>18233</v>
+      </c>
+      <c r="B57">
+        <v>118</v>
+      </c>
+      <c r="C57" s="6">
+        <v>126.66666666666667</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.7">
       <c r="C58" s="6"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A60" s="3" t="e" cm="1" vm="1">
+      <c r="A60" s="3" t="e" cm="1" vm="19">
         <f t="array" ref="A60">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A86" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A86">_xlfn._xlws.PY(5,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B86" s="5"/>
+      <c r="A86" s="3" t="str" cm="1">
+        <f t="array" ref="A86:B101">_xlfn._xlws.PY(5,0)</f>
+        <v>date</v>
+      </c>
+      <c r="B86" s="5" t="str">
+        <v>trend</v>
+      </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B87" s="5"/>
+      <c r="A87" s="3" vm="1">
+        <v>17899</v>
+      </c>
+      <c r="B87" s="5" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B88" s="5"/>
+      <c r="A88" s="3" vm="2">
+        <v>17930</v>
+      </c>
+      <c r="B88" s="5" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B89" s="5"/>
+      <c r="A89" s="3" vm="3">
+        <v>17958</v>
+      </c>
+      <c r="B89" s="5" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B90" s="5"/>
+      <c r="A90" s="3" vm="4">
+        <v>17989</v>
+      </c>
+      <c r="B90" s="5" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B91" s="5"/>
+      <c r="A91" s="3" vm="5">
+        <v>18019</v>
+      </c>
+      <c r="B91" s="5" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B92" s="5"/>
+      <c r="A92" s="3" vm="12">
+        <v>18050</v>
+      </c>
+      <c r="B92" s="5" t="e">
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B93" s="5"/>
+      <c r="A93" s="3" vm="13">
+        <v>18080</v>
+      </c>
+      <c r="B93" s="5">
+        <v>126.79166666666666</v>
+      </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B94" s="5"/>
+      <c r="A94" s="3" vm="14">
+        <v>18111</v>
+      </c>
+      <c r="B94" s="5">
+        <v>127.24999999999999</v>
+      </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B95" s="5"/>
+      <c r="A95" s="3" vm="15">
+        <v>18142</v>
+      </c>
+      <c r="B95" s="5">
+        <v>127.95833333333331</v>
+      </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B96" s="5"/>
+      <c r="A96" s="3" vm="16">
+        <v>18172</v>
+      </c>
+      <c r="B96" s="5">
+        <v>128.58333333333331</v>
+      </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B97" s="5"/>
+      <c r="A97" s="3" vm="17">
+        <v>18203</v>
+      </c>
+      <c r="B97" s="5">
+        <v>128.99999999999997</v>
+      </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B98" s="5"/>
+      <c r="A98" s="3" vm="18">
+        <v>18233</v>
+      </c>
+      <c r="B98" s="5">
+        <v>129.75</v>
+      </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B99" s="5"/>
+      <c r="A99" s="3" vm="20">
+        <v>18264</v>
+      </c>
+      <c r="B99" s="5">
+        <v>131.25</v>
+      </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B100" s="5"/>
+      <c r="A100" s="3" vm="21">
+        <v>18295</v>
+      </c>
+      <c r="B100" s="5">
+        <v>133.08333333333334</v>
+      </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B101" s="5"/>
+      <c r="A101" s="3" vm="22">
+        <v>18323</v>
+      </c>
+      <c r="B101" s="5">
+        <v>134.91666666666669</v>
+      </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A104" s="3" t="e" cm="1" vm="1">
+      <c r="A104" s="3" t="e" cm="1" vm="23">
         <f t="array" ref="A104">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.7">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.7">
       <c r="B119" s="6"/>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A120" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A120">_xlfn._xlws.PY(7,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B120" s="6"/>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B121" s="6"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B122" s="6"/>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B123" s="6"/>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B124" s="6"/>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B125" s="6"/>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B126" s="6"/>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B127" s="6"/>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B128" s="6"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B129" s="6"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B130" s="6"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A132" s="3" t="e" cm="1" vm="1">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A120" s="3" t="str" cm="1">
+        <f t="array" ref="A120:C131">_xlfn._xlws.PY(7,0)</f>
+        <v/>
+      </c>
+      <c r="B120" s="6" t="str">
+        <v>passengers</v>
+      </c>
+      <c r="C120" t="str">
+        <v>fitted</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A121" s="3" t="str">
+        <v>date</v>
+      </c>
+      <c r="B121" s="6" t="str">
+        <v/>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A122" s="3" vm="1">
+        <v>17899</v>
+      </c>
+      <c r="B122" s="6">
+        <v>112</v>
+      </c>
+      <c r="C122">
+        <v>111.95999796199298</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A123" s="3" vm="2">
+        <v>17930</v>
+      </c>
+      <c r="B123" s="6">
+        <v>118</v>
+      </c>
+      <c r="C123">
+        <v>120.19333660189936</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A124" s="3" vm="3">
+        <v>17958</v>
+      </c>
+      <c r="B124" s="6">
+        <v>132</v>
+      </c>
+      <c r="C124">
+        <v>134.67683544691363</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A125" s="3" vm="4">
+        <v>17989</v>
+      </c>
+      <c r="B125" s="6">
+        <v>129</v>
+      </c>
+      <c r="C125">
+        <v>131.40726345798356</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A126" s="3" vm="5">
+        <v>18019</v>
+      </c>
+      <c r="B126" s="6">
+        <v>121</v>
+      </c>
+      <c r="C126">
+        <v>124.64374307768698</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A127" s="3" vm="12">
+        <v>18050</v>
+      </c>
+      <c r="B127" s="6">
+        <v>135</v>
+      </c>
+      <c r="C127">
+        <v>140.4272455247596</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A128" s="3" vm="13">
+        <v>18080</v>
+      </c>
+      <c r="B128" s="6">
+        <v>148</v>
+      </c>
+      <c r="C128">
+        <v>153.85808678698692</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A129" s="3" vm="14">
+        <v>18111</v>
+      </c>
+      <c r="B129" s="6">
+        <v>148</v>
+      </c>
+      <c r="C129">
+        <v>152.4364177143994</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A130" s="3" vm="15">
+        <v>18142</v>
+      </c>
+      <c r="B130" s="6">
+        <v>136</v>
+      </c>
+      <c r="C130">
+        <v>139.68358943158842</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A131" s="3" vm="16">
+        <v>18172</v>
+      </c>
+      <c r="B131">
+        <v>119</v>
+      </c>
+      <c r="C131">
+        <v>122.38855242329556</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A132" s="3" t="e" cm="1" vm="24">
         <f t="array" ref="A132">_xlfn._xlws.PY(8,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A136" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A136">_xlfn._xlws.PY(9,0)</f>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A136" s="3" t="e" cm="1" vm="25">
+        <f t="array" aca="1" ref="A136" ca="1">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A138" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A138">_xlfn._xlws.PY(10,0)</f>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A138" s="3" t="e" cm="1" vm="26">
+        <f t="array" aca="1" ref="A138" ca="1">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A145" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A145">_xlfn._xlws.PY(11,0)</f>
+      <c r="A145" s="3" t="e" cm="1" vm="25">
+        <f t="array" aca="1" ref="A145" ca="1">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A153" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A153">_xlfn._xlws.PY(12,0)</f>
+      <c r="A153" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A153:B155" ca="1">_xlfn._xlws.PY(12,0)</f>
+        <v>Metric</v>
+      </c>
+      <c r="B153" t="str">
+        <f ca="1"/>
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A154" s="3" t="str">
+        <f ca="1"/>
+        <v>Test Statistic</v>
+      </c>
+      <c r="B154" s="6">
+        <f ca="1"/>
+        <v>0.81536887920606549</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A155" s="3" t="str">
+        <f ca="1"/>
+        <v>p-value</v>
+      </c>
+      <c r="B155" s="6">
+        <f ca="1"/>
+        <v>0.99188024343764125</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A157" s="3" t="e" cm="1" vm="28">
+        <f t="array" aca="1" ref="A157" ca="1">_xlfn._xlws.PY(13,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B154" s="6"/>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="B155" s="6"/>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A157" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A157">_xlfn._xlws.PY(13,1)</f>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A159" s="3" t="e" cm="1" vm="29">
+        <f t="array" aca="1" ref="A159" ca="1">_xlfn._xlws.PY(14,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A159" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A159">_xlfn._xlws.PY(14,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A161" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A161">_xlfn._xlws.PY(15,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B161" s="6"/>
+      <c r="A161" s="3" cm="1" vm="30">
+        <f t="array" aca="1" ref="A161:B165" ca="1">_xlfn._xlws.PY(15,0)</f>
+        <v>21551</v>
+      </c>
+      <c r="B161" s="6">
+        <f ca="1"/>
+        <v>354.17364147573602</v>
+      </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B162" s="6"/>
+      <c r="A162" s="3" vm="31">
+        <f ca="1"/>
+        <v>21582</v>
+      </c>
+      <c r="B162" s="6">
+        <f ca="1"/>
+        <v>337.57319653024558</v>
+      </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B163" s="6"/>
+      <c r="A163" s="3" vm="32">
+        <f ca="1"/>
+        <v>21610</v>
+      </c>
+      <c r="B163" s="6">
+        <f ca="1"/>
+        <v>387.7744448625624</v>
+      </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B164" s="6"/>
+      <c r="A164" s="3" vm="33">
+        <f ca="1"/>
+        <v>21641</v>
+      </c>
+      <c r="B164" s="6">
+        <f ca="1"/>
+        <v>379.77500904445122</v>
+      </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B165" s="6"/>
+      <c r="A165" s="3" vm="34">
+        <f ca="1"/>
+        <v>21671</v>
+      </c>
+      <c r="B165" s="6">
+        <f ca="1"/>
+        <v>397.21314537513348</v>
+      </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A168" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A168">_xlfn._xlws.PY(16,1)</f>
-        <v>#VALUE!</v>
+      <c r="A168" s="3" t="str" cm="1" vm="35">
+        <f t="array" aca="1" ref="A168" ca="1">_xlfn._xlws.PY(16,1)</f>
+        <v>Mean Absolute Error: 31.07</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A171" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A171">_xlfn._xlws.PY(17,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
+      <c r="A171" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A171:C183" ca="1">_xlfn._xlws.PY(17,0)</f>
+        <v>Actual</v>
+      </c>
+      <c r="B171" s="6" t="str">
+        <f ca="1"/>
+        <v>Forecast</v>
+      </c>
+      <c r="C171" s="6" t="str">
+        <f ca="1"/>
+        <v>Error</v>
+      </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
+      <c r="A172" s="3">
+        <f ca="1"/>
+        <v>360</v>
+      </c>
+      <c r="B172" s="6">
+        <f ca="1"/>
+        <v>354.17364147573602</v>
+      </c>
+      <c r="C172" s="6">
+        <f ca="1"/>
+        <v>5.8263585242639806</v>
+      </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
+      <c r="A173" s="3">
+        <f ca="1"/>
+        <v>342</v>
+      </c>
+      <c r="B173" s="6">
+        <f ca="1"/>
+        <v>337.57319653024558</v>
+      </c>
+      <c r="C173" s="6">
+        <f ca="1"/>
+        <v>4.4268034697544181</v>
+      </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
+      <c r="A174" s="3">
+        <f ca="1"/>
+        <v>406</v>
+      </c>
+      <c r="B174" s="6">
+        <f ca="1"/>
+        <v>387.7744448625624</v>
+      </c>
+      <c r="C174" s="6">
+        <f ca="1"/>
+        <v>18.225555137437595</v>
+      </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
+      <c r="A175" s="3">
+        <f ca="1"/>
+        <v>396</v>
+      </c>
+      <c r="B175" s="6">
+        <f ca="1"/>
+        <v>379.77500904445122</v>
+      </c>
+      <c r="C175" s="6">
+        <f ca="1"/>
+        <v>16.224990955548776</v>
+      </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
+      <c r="A176" s="3">
+        <f ca="1"/>
+        <v>420</v>
+      </c>
+      <c r="B176" s="6">
+        <f ca="1"/>
+        <v>397.21314537513348</v>
+      </c>
+      <c r="C176" s="6">
+        <f ca="1"/>
+        <v>22.786854624866521</v>
+      </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
+      <c r="A177" s="3">
+        <f ca="1"/>
+        <v>472</v>
+      </c>
+      <c r="B177" s="6">
+        <f ca="1"/>
+        <v>468.87706028701018</v>
+      </c>
+      <c r="C177" s="6">
+        <f ca="1"/>
+        <v>3.1229397129898189</v>
+      </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
+      <c r="A178" s="3">
+        <f ca="1"/>
+        <v>548</v>
+      </c>
+      <c r="B178" s="6">
+        <f ca="1"/>
+        <v>520.42527545650694</v>
+      </c>
+      <c r="C178" s="6">
+        <f ca="1"/>
+        <v>27.574724543493062</v>
+      </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
+      <c r="A179" s="3">
+        <f ca="1"/>
+        <v>559</v>
+      </c>
+      <c r="B179" s="6">
+        <f ca="1"/>
+        <v>526.51011146486042</v>
+      </c>
+      <c r="C179" s="6">
+        <f ca="1"/>
+        <v>32.489888535139585</v>
+      </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
+      <c r="A180" s="3">
+        <f ca="1"/>
+        <v>463</v>
+      </c>
+      <c r="B180" s="6">
+        <f ca="1"/>
+        <v>427.87427734740862</v>
+      </c>
+      <c r="C180" s="6">
+        <f ca="1"/>
+        <v>35.125722652591378</v>
+      </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
+      <c r="A181" s="3">
+        <f ca="1"/>
+        <v>407</v>
+      </c>
+      <c r="B181" s="6">
+        <f ca="1"/>
+        <v>381.94210181918794</v>
+      </c>
+      <c r="C181" s="6">
+        <f ca="1"/>
+        <v>25.05789818081206</v>
+      </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
+      <c r="A182" s="3">
+        <f ca="1"/>
+        <v>362</v>
+      </c>
+      <c r="B182" s="6">
+        <f ca="1"/>
+        <v>334.44886906567876</v>
+      </c>
+      <c r="C182" s="6">
+        <f ca="1"/>
+        <v>27.551130934321236</v>
+      </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
+      <c r="A183" s="3">
+        <f ca="1"/>
+        <v>405</v>
+      </c>
+      <c r="B183" s="6">
+        <f ca="1"/>
+        <v>373.5830131238987</v>
+      </c>
+      <c r="C183" s="6">
+        <f ca="1"/>
+        <v>31.416986876101305</v>
+      </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A187" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A187">_xlfn._xlws.PY(18,1)</f>
-        <v>#VALUE!</v>
+      <c r="A187" s="3" cm="1" vm="36">
+        <f t="array" aca="1" ref="A187" ca="1">_xlfn._xlws.PY(18,1)</f>
+        <v>115.25</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A190" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A190">_xlfn._xlws.PY(19,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.7">
-      <c r="A196" s="3" t="e" cm="1" vm="1">
-        <f t="array" ref="A196">_xlfn._xlws.PY(20,0)</f>
+      <c r="A190" s="3" t="str" cm="1">
+        <f t="array" aca="1" ref="A190:B193" ca="1">_xlfn._xlws.PY(19,0)</f>
+        <v>Metric</v>
+      </c>
+      <c r="B190" t="str">
+        <f ca="1"/>
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A191" s="3" t="str">
+        <f ca="1"/>
+        <v>Holt-Winters MAE</v>
+      </c>
+      <c r="B191">
+        <f ca="1"/>
+        <v>31.07</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.7">
+      <c r="A192" s="3" t="str">
+        <f ca="1"/>
+        <v>Baseline MAE</v>
+      </c>
+      <c r="B192">
+        <f ca="1"/>
+        <v>115.25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A193" s="3" t="str">
+        <f ca="1"/>
+        <v>Improvement (%)</v>
+      </c>
+      <c r="B193">
+        <f ca="1"/>
+        <v>73.040000000000006</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A196" s="3" t="e" cm="1" vm="37">
+        <f t="array" aca="1" ref="A196" ca="1">_xlfn._xlws.PY(20,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3966,27 +5355,91 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93D36D00-A3A2-41DD-AB6F-6740B077CEDA}">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.7">
-      <c r="A1" t="e" cm="1" vm="1">
-        <f t="array" ref="A1">_xlfn._xlws.PY(21,0,shampoo[#All])</f>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A1" t="str" cm="1">
+        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(21,0,shampoo[#All])</f>
+        <v/>
+      </c>
+      <c r="B1" t="str">
+        <f ca="1"/>
+        <v>sales</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A2" t="str">
+        <f ca="1"/>
+        <v>date</v>
+      </c>
+      <c r="B2" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A3" vm="38">
+        <f ca="1"/>
+        <v>36526</v>
+      </c>
+      <c r="B3">
+        <f ca="1"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A4" vm="39">
+        <f ca="1"/>
+        <v>36557</v>
+      </c>
+      <c r="B4">
+        <f ca="1"/>
+        <v>145.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A5" vm="40">
+        <f ca="1"/>
+        <v>36586</v>
+      </c>
+      <c r="B5">
+        <f ca="1"/>
+        <v>183.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A6" vm="41">
+        <f ca="1"/>
+        <v>36617</v>
+      </c>
+      <c r="B6">
+        <f ca="1"/>
+        <v>119.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A7" vm="42">
+        <f ca="1"/>
+        <v>36647</v>
+      </c>
+      <c r="B7">
+        <f ca="1"/>
+        <v>180.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.7">
+      <c r="A10" t="e" cm="1" vm="43">
+        <f t="array" aca="1" ref="A10" ca="1">_xlfn._xlws.PY(22,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.7">
-      <c r="A10" t="e" cm="1" vm="1">
-        <f t="array" ref="A10">_xlfn._xlws.PY(22,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.7">
-      <c r="A24" t="e" cm="1" vm="1">
-        <f t="array" ref="A24">_xlfn._xlws.PY(23,0)</f>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.7">
+      <c r="A27" t="e" cm="1" vm="44">
+        <f t="array" aca="1" ref="A27" ca="1">_xlfn._xlws.PY(23,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>

--- a/ch_07_forecasting_time_series/ch_07_solutions.xlsx
+++ b/ch_07_forecasting_time_series/ch_07_solutions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_07_forecasting_time_series\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B81526-F8A4-4EAD-B418-4B548E2947B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C632B75-B256-4746-9F32-2E261DDAA222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" firstSheet="1" activeTab="3" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" firstSheet="1" activeTab="1" xr2:uid="{127BCBE3-2501-4C38-9896-5064F2DA9264}"/>
   </bookViews>
   <sheets>
     <sheet name="AirPassengers" sheetId="1" r:id="rId1"/>
@@ -1733,10 +1733,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2193,101 +2193,104 @@
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
 <rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="51">
   <rv s="0">
+    <v>14</v>
+  </rv>
+  <rv s="1">
     <fb>17899</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17930</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17958</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17989</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18019</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>17988</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18079</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18171</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18263</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18353</fb>
     <v>0</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>0</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18050</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18080</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18111</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18142</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18172</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18203</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18233</fb>
     <v>0</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>1</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18264</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18295</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>18323</fb>
     <v>0</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>2</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="2">
+  <rv s="3">
     <v>&lt;class 'pandas.core.indexes.datetimes.DatetimeIndex'&gt;</v>
     <v>DatetimeIndex</v>
     <v>DatetimeIndex(['1961-01-01', '1961-02-01', '1961-03-01', '1961-04-01',
@@ -2296,57 +2299,54 @@
                '1962-01-01', '1962-02-0...</v>
     <v>1</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>3</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>0</v>
     <v>8</v>
     <v>23</v>
     <v>1</v>
   </rv>
-  <rv s="4">
-    <v>14</v>
-  </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21551</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21582</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21610</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21641</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>21671</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22129</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22160</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22190</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22221</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>22251</fb>
     <v>0</v>
   </rv>
@@ -2371,7 +2371,7 @@
     <v>38</v>
     <v>1</v>
   </rv>
-  <rv s="2">
+  <rv s="3">
     <v>&lt;class 'statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper'&gt;</v>
     <v>HoltWintersResultsWrapper</v>
     <v>&lt;statsmodels.tsa.holtwinters.results.HoltWintersResultsWrapper object at 0x7f63d8a76900&gt;</v>
@@ -2393,37 +2393,37 @@
     <v>115.25</v>
     <v>1</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>4</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36526</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36557</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36586</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36617</fb>
     <v>0</v>
   </rv>
-  <rv s="0">
+  <rv s="1">
     <fb>36647</fb>
     <v>0</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>5</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="1">
+  <rv s="2">
     <v>6</v>
     <v>9</v>
     <v>Image generated by Python</v>
@@ -2433,6 +2433,9 @@
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
 <rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="10">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+  </s>
   <s t="_formattednumber">
     <k n="_Format" t="spb"/>
   </s>
@@ -2452,9 +2455,6 @@
     <k n="errorType" t="i"/>
     <k n="rwOffset" t="i"/>
     <k n="subType" t="i"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
   </s>
   <s t="_array">
     <k n="array" t="a"/>
@@ -2565,7 +2565,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7FEE9AA1-77C4-44CB-80EC-CCEE1A5E4B85}" name="passengers" displayName="passengers" ref="A1:B145" totalsRowShown="0">
   <autoFilter ref="A1:B145" xr:uid="{7FEE9AA1-77C4-44CB-80EC-CCEE1A5E4B85}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{89C61804-E37F-46DC-843D-09FC2BF32AF1}" name="date" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{89C61804-E37F-46DC-843D-09FC2BF32AF1}" name="date" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{D51D0BEF-BFC7-4F34-B98C-315FEBBB8A48}" name="passengers"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2576,7 +2576,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8070347D-7673-46D1-8207-A1D784ACEE59}" name="shampoo" displayName="shampoo" ref="A1:B37" totalsRowShown="0">
   <autoFilter ref="A1:B37" xr:uid="{8070347D-7673-46D1-8207-A1D784ACEE59}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4511BAD2-C5B8-4115-8ECF-666BFDD2B720}" name="date" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{4511BAD2-C5B8-4115-8ECF-666BFDD2B720}" name="date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{1B629950-5F4A-4F2E-B795-D39EC6984B40}" name="sales"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4089,276 +4089,343 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A1" s="3" t="str" cm="1">
-        <f t="array" ref="A1:B7">_xlfn._xlws.PY(0,0,passengers[#All])</f>
+        <f t="array" aca="1" ref="A1:B7" ca="1">_xlfn._xlws.PY(0,0,passengers[#All])</f>
         <v/>
       </c>
       <c r="B1" t="str">
+        <f ca="1"/>
         <v>passengers</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A2" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B2" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A3" s="3" vm="1">
+      <c r="A3" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
       <c r="B3">
+        <f ca="1"/>
         <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A4" s="3" vm="2">
+      <c r="A4" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
       <c r="B4">
+        <f ca="1"/>
         <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A5" s="3" vm="3">
+      <c r="A5" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
       <c r="B5">
+        <f ca="1"/>
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A6" s="3" vm="4">
+      <c r="A6" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
       <c r="B6">
+        <f ca="1"/>
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A7" s="3" vm="5">
+      <c r="A7" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
       <c r="B7">
+        <f ca="1"/>
         <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A9" s="3" t="str" cm="1">
-        <f t="array" ref="A9:B15">_xlfn._xlws.PY(1,0)</f>
+        <f t="array" aca="1" ref="A9:B15" ca="1">_xlfn._xlws.PY(1,0)</f>
         <v/>
       </c>
       <c r="B9" t="str">
+        <f ca="1"/>
         <v>passengers</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A10" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B10" s="6" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A11" s="3" vm="6">
+      <c r="A11" s="3" vm="7">
+        <f ca="1"/>
         <v>17988</v>
       </c>
       <c r="B11" s="6">
+        <f ca="1"/>
         <v>120.66666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A12" s="3" vm="7">
+      <c r="A12" s="3" vm="8">
+        <f ca="1"/>
         <v>18079</v>
       </c>
       <c r="B12" s="6">
+        <f ca="1"/>
         <v>128.33333333333334</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A13" s="3" vm="8">
+      <c r="A13" s="3" vm="9">
+        <f ca="1"/>
         <v>18171</v>
       </c>
       <c r="B13" s="6">
+        <f ca="1"/>
         <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A14" s="3" vm="9">
+      <c r="A14" s="3" vm="10">
+        <f ca="1"/>
         <v>18263</v>
       </c>
       <c r="B14" s="6">
+        <f ca="1"/>
         <v>113.66666666666667</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A15" s="3" vm="10">
+      <c r="A15" s="3" vm="11">
+        <f ca="1"/>
         <v>18353</v>
       </c>
       <c r="B15" s="6">
+        <f ca="1"/>
         <v>127.33333333333333</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.7">
-      <c r="A17" s="3" t="e" cm="1" vm="11">
-        <f t="array" ref="A17">_xlfn._xlws.PY(2,0)</f>
+      <c r="A17" s="3" t="e" cm="1" vm="12">
+        <f t="array" aca="1" ref="A17" ca="1">_xlfn._xlws.PY(2,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A44" s="3" t="str" cm="1">
-        <f t="array" ref="A44:C57">_xlfn._xlws.PY(3,0)</f>
+        <f t="array" aca="1" ref="A44:C57" ca="1">_xlfn._xlws.PY(3,0)</f>
         <v/>
       </c>
       <c r="B44" t="str">
+        <f ca="1"/>
         <v>passengers</v>
       </c>
       <c r="C44" s="6" t="str">
+        <f ca="1"/>
         <v>rolling_mean</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A45" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B45" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="C45" s="6" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A46" s="3" vm="1">
+      <c r="A46" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
       <c r="B46">
+        <f ca="1"/>
         <v>112</v>
       </c>
       <c r="C46" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A47" s="3" vm="2">
+      <c r="A47" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
       <c r="B47">
+        <f ca="1"/>
         <v>118</v>
       </c>
       <c r="C47" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A48" s="3" vm="3">
+      <c r="A48" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
       <c r="B48">
+        <f ca="1"/>
         <v>132</v>
       </c>
       <c r="C48" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A49" s="3" vm="4">
+      <c r="A49" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
       <c r="B49">
+        <f ca="1"/>
         <v>129</v>
       </c>
       <c r="C49" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A50" s="3" vm="5">
+      <c r="A50" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
       <c r="B50">
+        <f ca="1"/>
         <v>121</v>
       </c>
       <c r="C50" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A51" s="3" vm="12">
+      <c r="A51" s="3" vm="13">
+        <f ca="1"/>
         <v>18050</v>
       </c>
       <c r="B51">
+        <f ca="1"/>
         <v>135</v>
       </c>
       <c r="C51" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A52" s="3" vm="13">
+      <c r="A52" s="3" vm="14">
+        <f ca="1"/>
         <v>18080</v>
       </c>
       <c r="B52">
+        <f ca="1"/>
         <v>148</v>
       </c>
       <c r="C52" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A53" s="3" vm="14">
+      <c r="A53" s="3" vm="15">
+        <f ca="1"/>
         <v>18111</v>
       </c>
       <c r="B53">
+        <f ca="1"/>
         <v>148</v>
       </c>
       <c r="C53" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A54" s="3" vm="15">
+      <c r="A54" s="3" vm="16">
+        <f ca="1"/>
         <v>18142</v>
       </c>
       <c r="B54">
+        <f ca="1"/>
         <v>136</v>
       </c>
       <c r="C54" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A55" s="3" vm="16">
+      <c r="A55" s="3" vm="17">
+        <f ca="1"/>
         <v>18172</v>
       </c>
       <c r="B55">
+        <f ca="1"/>
         <v>119</v>
       </c>
       <c r="C55" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A56" s="3" vm="17">
+      <c r="A56" s="3" vm="18">
+        <f ca="1"/>
         <v>18203</v>
       </c>
       <c r="B56">
+        <f ca="1"/>
         <v>104</v>
       </c>
       <c r="C56" s="6" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A57" s="3" vm="18">
+      <c r="A57" s="3" vm="19">
+        <f ca="1"/>
         <v>18233</v>
       </c>
       <c r="B57">
+        <f ca="1"/>
         <v>118</v>
       </c>
       <c r="C57" s="6">
+        <f ca="1"/>
         <v>126.66666666666667</v>
       </c>
     </row>
@@ -4366,143 +4433,174 @@
       <c r="C58" s="6"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A60" s="3" t="e" cm="1" vm="19">
-        <f t="array" ref="A60">_xlfn._xlws.PY(4,0)</f>
+      <c r="A60" s="3" t="e" cm="1" vm="20">
+        <f t="array" aca="1" ref="A60" ca="1">_xlfn._xlws.PY(4,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.7">
       <c r="A86" s="3" t="str" cm="1">
-        <f t="array" ref="A86:B101">_xlfn._xlws.PY(5,0)</f>
+        <f t="array" aca="1" ref="A86:B101" ca="1">_xlfn._xlws.PY(5,0)</f>
         <v>date</v>
       </c>
       <c r="B86" s="5" t="str">
+        <f ca="1"/>
         <v>trend</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A87" s="3" vm="1">
+      <c r="A87" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
       <c r="B87" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A88" s="3" vm="2">
+      <c r="A88" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
       <c r="B88" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A89" s="3" vm="3">
+      <c r="A89" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
       <c r="B89" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A90" s="3" vm="4">
+      <c r="A90" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
       <c r="B90" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A91" s="3" vm="5">
+      <c r="A91" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
       <c r="B91" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A92" s="3" vm="12">
+      <c r="A92" s="3" vm="13">
+        <f ca="1"/>
         <v>18050</v>
       </c>
       <c r="B92" s="5" t="e">
+        <f ca="1"/>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A93" s="3" vm="13">
+      <c r="A93" s="3" vm="14">
+        <f ca="1"/>
         <v>18080</v>
       </c>
       <c r="B93" s="5">
+        <f ca="1"/>
         <v>126.79166666666666</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A94" s="3" vm="14">
+      <c r="A94" s="3" vm="15">
+        <f ca="1"/>
         <v>18111</v>
       </c>
       <c r="B94" s="5">
+        <f ca="1"/>
         <v>127.24999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A95" s="3" vm="15">
+      <c r="A95" s="3" vm="16">
+        <f ca="1"/>
         <v>18142</v>
       </c>
       <c r="B95" s="5">
+        <f ca="1"/>
         <v>127.95833333333331</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A96" s="3" vm="16">
+      <c r="A96" s="3" vm="17">
+        <f ca="1"/>
         <v>18172</v>
       </c>
       <c r="B96" s="5">
+        <f ca="1"/>
         <v>128.58333333333331</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A97" s="3" vm="17">
+      <c r="A97" s="3" vm="18">
+        <f ca="1"/>
         <v>18203</v>
       </c>
       <c r="B97" s="5">
+        <f ca="1"/>
         <v>128.99999999999997</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A98" s="3" vm="18">
+      <c r="A98" s="3" vm="19">
+        <f ca="1"/>
         <v>18233</v>
       </c>
       <c r="B98" s="5">
+        <f ca="1"/>
         <v>129.75</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A99" s="3" vm="20">
+      <c r="A99" s="3" vm="21">
+        <f ca="1"/>
         <v>18264</v>
       </c>
       <c r="B99" s="5">
+        <f ca="1"/>
         <v>131.25</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A100" s="3" vm="21">
+      <c r="A100" s="3" vm="22">
+        <f ca="1"/>
         <v>18295</v>
       </c>
       <c r="B100" s="5">
+        <f ca="1"/>
         <v>133.08333333333334</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A101" s="3" vm="22">
+      <c r="A101" s="3" vm="23">
+        <f ca="1"/>
         <v>18323</v>
       </c>
       <c r="B101" s="5">
+        <f ca="1"/>
         <v>134.91666666666669</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A104" s="3" t="e" cm="1" vm="23">
-        <f t="array" ref="A104">_xlfn._xlws.PY(6,0)</f>
+      <c r="A104" s="3" t="e" cm="1" vm="24">
+        <f t="array" aca="1" ref="A104" ca="1">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -4511,157 +4609,192 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A120" s="3" t="str" cm="1">
-        <f t="array" ref="A120:C131">_xlfn._xlws.PY(7,0)</f>
+        <f t="array" aca="1" ref="A120:C131" ca="1">_xlfn._xlws.PY(7,0)</f>
         <v/>
       </c>
       <c r="B120" s="6" t="str">
+        <f ca="1"/>
         <v>passengers</v>
       </c>
       <c r="C120" t="str">
+        <f ca="1"/>
         <v>fitted</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.7">
       <c r="A121" s="3" t="str">
+        <f ca="1"/>
         <v>date</v>
       </c>
       <c r="B121" s="6" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="C121" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A122" s="3" vm="1">
+      <c r="A122" s="3" vm="2">
+        <f ca="1"/>
         <v>17899</v>
       </c>
       <c r="B122" s="6">
+        <f ca="1"/>
         <v>112</v>
       </c>
       <c r="C122">
+        <f ca="1"/>
         <v>111.95999796199298</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A123" s="3" vm="2">
+      <c r="A123" s="3" vm="3">
+        <f ca="1"/>
         <v>17930</v>
       </c>
       <c r="B123" s="6">
+        <f ca="1"/>
         <v>118</v>
       </c>
       <c r="C123">
+        <f ca="1"/>
         <v>120.19333660189936</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A124" s="3" vm="3">
+      <c r="A124" s="3" vm="4">
+        <f ca="1"/>
         <v>17958</v>
       </c>
       <c r="B124" s="6">
+        <f ca="1"/>
         <v>132</v>
       </c>
       <c r="C124">
+        <f ca="1"/>
         <v>134.67683544691363</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A125" s="3" vm="4">
+      <c r="A125" s="3" vm="5">
+        <f ca="1"/>
         <v>17989</v>
       </c>
       <c r="B125" s="6">
+        <f ca="1"/>
         <v>129</v>
       </c>
       <c r="C125">
+        <f ca="1"/>
         <v>131.40726345798356</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A126" s="3" vm="5">
+      <c r="A126" s="3" vm="6">
+        <f ca="1"/>
         <v>18019</v>
       </c>
       <c r="B126" s="6">
+        <f ca="1"/>
         <v>121</v>
       </c>
       <c r="C126">
+        <f ca="1"/>
         <v>124.64374307768698</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A127" s="3" vm="12">
+      <c r="A127" s="3" vm="13">
+        <f ca="1"/>
         <v>18050</v>
       </c>
       <c r="B127" s="6">
+        <f ca="1"/>
         <v>135</v>
       </c>
       <c r="C127">
+        <f ca="1"/>
         <v>140.4272455247596</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A128" s="3" vm="13">
+      <c r="A128" s="3" vm="14">
+        <f ca="1"/>
         <v>18080</v>
       </c>
       <c r="B128" s="6">
+        <f ca="1"/>
         <v>148</v>
       </c>
       <c r="C128">
+        <f ca="1"/>
         <v>153.85808678698692</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A129" s="3" vm="14">
+      <c r="A129" s="3" vm="15">
+        <f ca="1"/>
         <v>18111</v>
       </c>
       <c r="B129" s="6">
+        <f ca="1"/>
         <v>148</v>
       </c>
       <c r="C129">
+        <f ca="1"/>
         <v>152.4364177143994</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A130" s="3" vm="15">
+      <c r="A130" s="3" vm="16">
+        <f ca="1"/>
         <v>18142</v>
       </c>
       <c r="B130" s="6">
+        <f ca="1"/>
         <v>136</v>
       </c>
       <c r="C130">
+        <f ca="1"/>
         <v>139.68358943158842</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A131" s="3" vm="16">
+      <c r="A131" s="3" vm="17">
+        <f ca="1"/>
         <v>18172</v>
       </c>
       <c r="B131">
+        <f ca="1"/>
         <v>119</v>
       </c>
       <c r="C131">
+        <f ca="1"/>
         <v>122.38855242329556</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A132" s="3" t="e" cm="1" vm="24">
-        <f t="array" ref="A132">_xlfn._xlws.PY(8,1)</f>
+      <c r="A132" s="3" t="e" cm="1" vm="25">
+        <f t="array" aca="1" ref="A132" ca="1">_xlfn._xlws.PY(8,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A136" s="3" t="e" cm="1" vm="25">
+      <c r="A136" s="3" t="e" cm="1" vm="26">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn._xlws.PY(9,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.7">
-      <c r="A138" s="3" t="e" cm="1" vm="26">
+      <c r="A138" s="3" t="e" cm="1" vm="27">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn._xlws.PY(10,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.7">
-      <c r="A145" s="3" t="e" cm="1" vm="25">
+      <c r="A145" s="3" t="e" cm="1" vm="26">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn._xlws.PY(11,0)</f>
         <v>#VALUE!</v>
       </c>
